--- a/results/job_matches_2026-03-25.xlsx
+++ b/results/job_matches_2026-03-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer III: DevOps</t>
+          <t>Data Engineer (GCP)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, Scala</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,137 +496,137 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed96ac951faf1fe</t>
+          <t>https://www.indeed.com/viewjob?jk=1224b5cebc9ca8bb</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud</t>
+          <t>Data Engineer (GCP)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bitdeer Technologies Group</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d17ff767cfe6de4</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc3a06012f008f3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Devops - Embedded Engineer - IOT</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Brillius</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, DynamoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e14322c45e210aa</t>
+          <t>https://www.indeed.com/viewjob?jk=69b516454f937a66</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Python and PySpark, No SQL Developer-1</t>
+          <t>Software Engineer III: DevOps</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=934a100fa2f03442</t>
+          <t>https://www.indeed.com/viewjob?jk=eed96ac951faf1fe</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Cloud Data Platform Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kiely Family of Companies</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tinton Falls, NJ, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL</t>
+          <t>Google Cloud Platform, GCP, Dataflow, Cloud Storage, Spark, Scala, Snowflake, NoSQL, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8ac6e29a223b095</t>
+          <t>https://www.indeed.com/viewjob?jk=815d21355bca9afb</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Devops - Embedded Engineer - IOT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kiely Family of Companies</t>
+          <t>Brillius</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tinton Falls, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,59 +671,59 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b2ba9ffb9a799d</t>
+          <t>https://www.indeed.com/viewjob?jk=7e14322c45e210aa</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior IT Analyst - Data Engineering</t>
+          <t>Python and PySpark, No SQL Developer-1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57867842740dcc59</t>
+          <t>https://www.indeed.com/viewjob?jk=934a100fa2f03442</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Kiely Family of Companies</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tinton Falls, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d2d9cf01e65cfd8</t>
+          <t>https://www.indeed.com/viewjob?jk=a8ac6e29a223b095</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Kiely Family of Companies</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tinton Falls, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,49 +776,49 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cec5fe386ea9e81</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b2ba9ffb9a799d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2fd5678c94e0e11</t>
+          <t>https://www.indeed.com/viewjob?jk=0d2d9cf01e65cfd8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Salesforce Service Cloud Specialist</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -832,11 +832,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c63d8ea7f769e54</t>
+          <t>https://www.indeed.com/viewjob?jk=1cec5fe386ea9e81</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Data Products</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Autodesk</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9e0e8ee32af5e56</t>
+          <t>https://www.indeed.com/viewjob?jk=d2fd5678c94e0e11</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Salesforce Service Cloud Specialist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Augment Professional Services</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform</t>
+          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e76e474f9e2efb6</t>
+          <t>https://www.indeed.com/viewjob?jk=8c63d8ea7f769e54</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70b82e4ad32cd227</t>
+          <t>https://www.indeed.com/viewjob?jk=d15957719609ec59</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IT Data Engineer - Level 3</t>
+          <t>Sr. Software Engineer, Data Products</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cintas</t>
+          <t>Autodesk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, Spark</t>
+          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2550c832064daf74</t>
+          <t>https://www.indeed.com/viewjob?jk=c9e0e8ee32af5e56</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IT Data Engineer - Level 3</t>
+          <t>Data Foundations Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cintas</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, Spark</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35633737b3f1427c</t>
+          <t>https://www.indeed.com/viewjob?jk=73966b170bd92bef</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Data Foundations Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5ed7b4a07ec36ef</t>
+          <t>https://www.indeed.com/viewjob?jk=f328d78d7b80a9bf</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Foundations Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Hadoop, Spark, PySpark, SQL Server, Data Modeling</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cec7ac1f3411b653</t>
+          <t>https://www.indeed.com/viewjob?jk=19cd66b829b5339a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - Java</t>
+          <t>Data Foundations Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Simplain Software Solutions LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Walnut, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eff7247decd592d</t>
+          <t>https://www.indeed.com/viewjob?jk=a15946806730eb5d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics and Visualization</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Also</t>
+          <t>Old National Bank</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Lake Elmo, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Databricks, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe62c0aa52bf9aa</t>
+          <t>https://www.indeed.com/viewjob?jk=f1ae7b8f4932aea6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python &amp; Snowflake)</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3Pillar Global</t>
+          <t>Augment Professional Services</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Snowflake, SQL Server, DynamoDB, dbt</t>
+          <t>AWS, Lambda, RDS, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff80065b4fd4799</t>
+          <t>https://www.indeed.com/viewjob?jk=4e76e474f9e2efb6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77901b3684582750</t>
+          <t>https://www.indeed.com/viewjob?jk=70b82e4ad32cd227</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Cloud - Platform Test</t>
+          <t>IT Data Engineer - Level 3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Cintas</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Jenkins</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4d5281c97057bc</t>
+          <t>https://www.indeed.com/viewjob?jk=2550c832064daf74</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>IT Data Engineer - Level 3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Elixir Technologies</t>
+          <t>Cintas</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ojai, CA, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline, Maven, Terraform</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,137 +1301,137 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a724ee3a9b6bd5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=35633737b3f1427c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Azure DevOps)</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Smart IMS</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Scala, Snowflake, MLOps, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e14868fa1c6b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=e5ed7b4a07ec36ef</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, MarTech</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Hadoop, Spark, PySpark, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1daebb30fd5fc85c</t>
+          <t>https://www.indeed.com/viewjob?jk=cec7ac1f3411b653</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DEVELOPER L3</t>
+          <t>Data Warehouse Architect + Security Czar</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>hr@brxio.com</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>North Quincy, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Hadoop, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72c2c42a5838eae6</t>
+          <t>https://www.indeed.com/viewjob?jk=a9cfc8c1e5c32169</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack Developer - Java</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Intellias</t>
+          <t>Simplain Software Solutions LLC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Walnut, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>S3, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c59056599f6669cd</t>
+          <t>https://www.indeed.com/viewjob?jk=0eff7247decd592d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IT AI&amp;S Senior Data Engineer</t>
+          <t>Senior Data Engineer - Analytics and Visualization</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>Also</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd7ea95be40f976</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe62c0aa52bf9aa</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Engineer (Python &amp; Snowflake)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ClickBank</t>
+          <t>3Pillar Global</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, RDS, Scala, MySQL, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Snowflake, SQL Server, DynamoDB, dbt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=412f3333e8a582ca</t>
+          <t>https://www.indeed.com/viewjob?jk=bff80065b4fd4799</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>IT AI&amp;S Senior Data Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e29bb5eef54aab18</t>
+          <t>https://www.indeed.com/viewjob?jk=d21a5637c26aeee6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Oxford Economics</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d76d14c5568ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=18d46da9a88bc799</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CD Excellence Data Engineering Associate</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Unilever</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c49b3555427c9f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=28ea1b73fd02e910</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Oxford Economics</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,67 +1651,67 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1782e281cbd34a</t>
+          <t>https://www.indeed.com/viewjob?jk=520267b51ab833b5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>The Shade Store</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80c249f67538f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=77901b3684582750</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr. Software Engineer, Cloud - Platform Test</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Intellias</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc90240b32e9d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4d5281c97057bc</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior AI Engineer, MarTech</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=103595c75d73a7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=1daebb30fd5fc85c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Intern - Cloud Engineer</t>
+          <t>DEVELOPER L3</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>North Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, Scala, Kafka, DynamoDB, NoSQL</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,102 +1791,102 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f194b7e973e71ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=72c2c42a5838eae6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Enterprise Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>Intellias</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Oracle, Jenkins, Terraform</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c76f242258bad842</t>
+          <t>https://www.indeed.com/viewjob?jk=c59056599f6669cd</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Engineer, Enterprise Data Management</t>
+          <t>IT AI&amp;S Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Delaware North</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, PySpark, Oracle, MySQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4b0fb16ab29222</t>
+          <t>https://www.indeed.com/viewjob?jk=9dd7ea95be40f976</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Consultant, Data Management</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Beghou Consulting</t>
+          <t>ClickBank</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, S3, SQS, SNS, IAM, RDS, Scala, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be506a2e3bc5ee78</t>
+          <t>https://www.indeed.com/viewjob?jk=412f3333e8a582ca</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>IT AI&amp;S Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mercari</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69b773db1c488113</t>
+          <t>https://www.indeed.com/viewjob?jk=e29bb5eef54aab18</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Oxford Economics</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fa1c79d7085ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d76d14c5568ea6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>CD Excellence Data Engineering Associate</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Unilever</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,242 +2001,242 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7e36064fcccf83f</t>
+          <t>https://www.indeed.com/viewjob?jk=c49b3555427c9f7a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>.NET Software Engineer</t>
+          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TraXtion</t>
+          <t>Oxford Economics</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f809df752b708e</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1782e281cbd34a</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SDET</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc49399df060bfe1</t>
+          <t>https://www.indeed.com/viewjob?jk=983aa41d463e2b8e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>LightEdge</t>
+          <t>The Shade Store</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d903df923be7974b</t>
+          <t>https://www.indeed.com/viewjob?jk=c80c249f67538f2f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RJW Logistics</t>
+          <t>Intellias</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00950f1140481fca</t>
+          <t>https://www.indeed.com/viewjob?jk=5fc90240b32e9d4a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Developer III - Application Development</t>
+          <t>Database Engineer with Java MS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
+          <t>AWS, ECS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f3984b03cd26c72</t>
+          <t>https://www.indeed.com/viewjob?jk=25b94269754a9820</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Owings Mills, MD, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b8eb10a2720f342</t>
+          <t>https://www.indeed.com/viewjob?jk=103595c75d73a7c1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Intern - Cloud Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, Scala, Kafka, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6767c0e89ecdbcae</t>
+          <t>https://www.indeed.com/viewjob?jk=f194b7e973e71ef2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GM Motorsports</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Mercari</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e18d9eef9566cc88</t>
+          <t>https://www.indeed.com/viewjob?jk=69b773db1c488113</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>El Dorado Hills, CA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
+          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c873a7854b5a7a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=65fa1c79d7085ebe</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>SDET</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Waséyabek Development Company</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Otsego, MI, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Azure, Kafka, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Scala, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=467fe0059b658cf7</t>
+          <t>https://www.indeed.com/viewjob?jk=bc49399df060bfe1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Plante Moran</t>
+          <t>LightEdge</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,164 +2386,164 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39cd370d20d11526</t>
+          <t>https://www.indeed.com/viewjob?jk=7bb7334f3f2d66e8</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>RJW Logistics</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Docker</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1074f4222424a549</t>
+          <t>https://www.indeed.com/viewjob?jk=00950f1140481fca</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr Business Data Analyst</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc24446fe258028</t>
+          <t>https://www.indeed.com/viewjob?jk=f7e36064fcccf83f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack (EAA - Compliance)</t>
+          <t>.NET Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>TraXtion</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, MongoDB, NoSQL, ETL, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4577a3ce998c3da0</t>
+          <t>https://www.indeed.com/viewjob?jk=24f809df752b708e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Developer III - Application Development</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c10749649c748ef</t>
+          <t>https://www.indeed.com/viewjob?jk=4f3984b03cd26c72</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Full Stack Developer Intern</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Westford, MA, US USA</t>
+          <t>Owings Mills, MD, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6d07eb218f7af80</t>
+          <t>https://www.indeed.com/viewjob?jk=4b8eb10a2720f342</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Quality Platform Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Circle.so</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,137 +2596,137 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=235baa8877534de1</t>
+          <t>https://www.indeed.com/viewjob?jk=6767c0e89ecdbcae</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II - AI Research</t>
+          <t>Senior Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ef7e9e1ea58ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=e18d9eef9566cc88</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II - AI Research</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07b8d90194afa03f</t>
+          <t>https://www.indeed.com/viewjob?jk=c873a7854b5a7a4a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II - AI Research</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Waséyabek Development Company</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Otsego, MI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>Azure, Kafka, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d172d2add04f64</t>
+          <t>https://www.indeed.com/viewjob?jk=467fe0059b658cf7</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer II - ML Platform</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Burlington Stores</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Edgewater Park, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
+          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d93e23fa17175252</t>
+          <t>https://www.indeed.com/viewjob?jk=6f38667e23fc2e6a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Fanatics</t>
+          <t>Plante Moran</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, RDS, Kafka, MongoDB, Tableau, CI/CD, Airflow</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,19 +2771,19 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5daf9a09c12e8d35</t>
+          <t>https://www.indeed.com/viewjob?jk=39cd370d20d11526</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Experienced Data &amp; AI Platform Cloud DevOps / DataOps Engineer</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2792,11 +2792,11 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Blob Storage, Unity Catalog, Scala, DataOps, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,67 +2806,67 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cbeb2be8c0c0a59</t>
+          <t>https://www.indeed.com/viewjob?jk=1074f4222424a549</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - Full Stack (EAA - Compliance)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>The Clearing House Payments Company</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Liberty, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Scala, Kafka, Tableau, CI/CD, Terraform, Git, Python</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, MongoDB, NoSQL, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beb95949bff9aca2</t>
+          <t>https://www.indeed.com/viewjob?jk=4577a3ce998c3da0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Engineer IV, Data Engineering</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Omnicell</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Python, SQL</t>
+          <t>Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46ffdeefe4f68e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=4c10749649c748ef</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Full Stack Developer Intern</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Westford, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7da3735857b8f1b1</t>
+          <t>https://www.indeed.com/viewjob?jk=e6d07eb218f7af80</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud - Test Platform</t>
+          <t>Senior Quality Platform Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Circle.so</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, Cassandra, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=089cf1934f4cd6a4</t>
+          <t>https://www.indeed.com/viewjob?jk=235baa8877534de1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GreenBox Capital</t>
+          <t>Burlington Stores</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Edgewater Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83d3f50fcc4de14e</t>
+          <t>https://www.indeed.com/viewjob?jk=d93e23fa17175252</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Fanatics</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Kinesis, Redshift, S3, RDS, Kafka, MongoDB, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d27208e71b125f4</t>
+          <t>https://www.indeed.com/viewjob?jk=5daf9a09c12e8d35</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Experienced Data &amp; AI Platform Cloud DevOps / DataOps Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Blob Storage, Unity Catalog, Scala, DataOps, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f423abaf086a5787</t>
+          <t>https://www.indeed.com/viewjob?jk=1cbeb2be8c0c0a59</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Developer III - Application Development (Data Integration)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>The Clearing House Payments Company</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Liberty, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,15 +3076,330 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
+          <t>AWS, Glue, Kinesis, Scala, Kafka, Tableau, CI/CD, Terraform, Git, Python</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=beb95949bff9aca2</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Enterprise Data Analytics and AI Developer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Dudek</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d343da250ebc576a</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Engineer IV, Data Engineering</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Omnicell</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46ffdeefe4f68e9e</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Solution Architect</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>HCA Healthcare</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7da3735857b8f1b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Sr. Engineer, Cloud - Test Platform</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Redmond, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Scala, Kafka, Cassandra, Jenkins, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=089cf1934f4cd6a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>GreenBox Capital</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83d3f50fcc4de14e</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d27208e71b125f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Senior Java Developer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Conduent</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f423abaf086a5787</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d37428d214fe7e4f</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Developer III - Application Development (Data Integration)</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Inland Empire Health Plan</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Rancho Cucamonga, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
           <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>2025-09-24</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ee815ea22a573add</t>
         </is>

--- a/results/job_matches_2026-03-25.xlsx
+++ b/results/job_matches_2026-03-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Live Nation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, API Gateway, RDS, Databricks, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,42 +951,42 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15957719609ec59</t>
+          <t>https://www.indeed.com/viewjob?jk=d2d1e17a962b5fca</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Data Products</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Autodesk</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9e0e8ee32af5e56</t>
+          <t>https://www.indeed.com/viewjob?jk=d15957719609ec59</t>
         </is>
       </c>
     </row>
@@ -1728,17 +1728,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, MarTech</t>
+          <t>DEVELOPER L3</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>North Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1daebb30fd5fc85c</t>
+          <t>https://www.indeed.com/viewjob?jk=72c2c42a5838eae6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DEVELOPER L3</t>
+          <t>Senior AI Engineer, MarTech</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>North Quincy, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72c2c42a5838eae6</t>
+          <t>https://www.indeed.com/viewjob?jk=1daebb30fd5fc85c</t>
         </is>
       </c>
     </row>
@@ -2358,17 +2358,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>LightEdge</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bb7334f3f2d66e8</t>
+          <t>https://www.indeed.com/viewjob?jk=f7e36064fcccf83f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>.NET Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>RJW Logistics</t>
+          <t>TraXtion</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00950f1140481fca</t>
+          <t>https://www.indeed.com/viewjob?jk=24f809df752b708e</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Developer III - Application Development</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7e36064fcccf83f</t>
+          <t>https://www.indeed.com/viewjob?jk=4f3984b03cd26c72</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>.NET Software Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>TraXtion</t>
+          <t>LightEdge</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f809df752b708e</t>
+          <t>https://www.indeed.com/viewjob?jk=7bb7334f3f2d66e8</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Developer III - Application Development</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>RJW Logistics</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,17 +2516,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f3984b03cd26c72</t>
+          <t>https://www.indeed.com/viewjob?jk=00950f1140481fca</t>
         </is>
       </c>
     </row>
@@ -2638,17 +2638,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Distinguished Architect, Data Platform</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>El Dorado Hills, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
+          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c873a7854b5a7a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd1095da2d18982</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Waséyabek Development Company</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Otsego, MI, US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Azure, Kafka, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=467fe0059b658cf7</t>
+          <t>https://www.indeed.com/viewjob?jk=c873a7854b5a7a4a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - ML Platform</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Waséyabek Development Company</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Otsego, MI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Kubernetes</t>
+          <t>Azure, Kafka, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f38667e23fc2e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=467fe0059b658cf7</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Software Development Engineer II - ML Platform</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Plante Moran</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39cd370d20d11526</t>
+          <t>https://www.indeed.com/viewjob?jk=6f38667e23fc2e6a</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Plante Moran</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Docker</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1074f4222424a549</t>
+          <t>https://www.indeed.com/viewjob?jk=39cd370d20d11526</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack (EAA - Compliance)</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, MongoDB, NoSQL, ETL, Terraform, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4577a3ce998c3da0</t>
+          <t>https://www.indeed.com/viewjob?jk=1074f4222424a549</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Software Engineer - Full Stack (EAA - Compliance)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, MongoDB, NoSQL, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c10749649c748ef</t>
+          <t>https://www.indeed.com/viewjob?jk=4577a3ce998c3da0</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Full Stack Developer Intern</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Westford, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
+          <t>Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6d07eb218f7af80</t>
+          <t>https://www.indeed.com/viewjob?jk=4c10749649c748ef</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Quality Platform Engineer</t>
+          <t>Full Stack Developer Intern</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Circle.so</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westford, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=235baa8877534de1</t>
+          <t>https://www.indeed.com/viewjob?jk=e6d07eb218f7af80</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Quality Platform Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Burlington Stores</t>
+          <t>Circle.so</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Edgewater Park, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d93e23fa17175252</t>
+          <t>https://www.indeed.com/viewjob?jk=235baa8877534de1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Fanatics</t>
+          <t>Burlington Stores</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Edgewater Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, RDS, Kafka, MongoDB, Tableau, CI/CD, Airflow</t>
+          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5daf9a09c12e8d35</t>
+          <t>https://www.indeed.com/viewjob?jk=d93e23fa17175252</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Experienced Data &amp; AI Platform Cloud DevOps / DataOps Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Fanatics</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Blob Storage, Unity Catalog, Scala, DataOps, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Kinesis, Redshift, S3, RDS, Kafka, MongoDB, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cbeb2be8c0c0a59</t>
+          <t>https://www.indeed.com/viewjob?jk=5daf9a09c12e8d35</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Experienced Data &amp; AI Platform Cloud DevOps / DataOps Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>The Clearing House Payments Company</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Liberty, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Scala, Kafka, Tableau, CI/CD, Terraform, Git, Python</t>
+          <t>RDS, Azure, Databricks, Blob Storage, Unity Catalog, Scala, DataOps, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beb95949bff9aca2</t>
+          <t>https://www.indeed.com/viewjob?jk=1cbeb2be8c0c0a59</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Enterprise Data Analytics and AI Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Dudek</t>
+          <t>The Clearing House Payments Company</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Liberty, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,17 +3111,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
+          <t>AWS, Glue, Kinesis, Scala, Kafka, Tableau, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d343da250ebc576a</t>
+          <t>https://www.indeed.com/viewjob?jk=beb95949bff9aca2</t>
         </is>
       </c>
     </row>
@@ -3233,12 +3233,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Enterprise Data Analytics and AI Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GreenBox Capital</t>
+          <t>Dudek</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83d3f50fcc4de14e</t>
+          <t>https://www.indeed.com/viewjob?jk=d343da250ebc576a</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>GreenBox Capital</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,19 +3296,19 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d27208e71b125f4</t>
+          <t>https://www.indeed.com/viewjob?jk=83d3f50fcc4de14e</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f423abaf086a5787</t>
+          <t>https://www.indeed.com/viewjob?jk=2d27208e71b125f4</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d37428d214fe7e4f</t>
+          <t>https://www.indeed.com/viewjob?jk=f423abaf086a5787</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Developer III - Application Development (Data Integration)</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,15 +3391,50 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d37428d214fe7e4f</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Developer III - Application Development (Data Integration)</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Inland Empire Health Plan</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Rancho Cucamonga, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
           <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>2025-09-24</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ee815ea22a573add</t>
         </is>

--- a/results/job_matches_2026-03-25.xlsx
+++ b/results/job_matches_2026-03-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - Java</t>
+          <t>Sr Data Scientist</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Simplain Software Solutions LLC</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Walnut, CA, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, Power BI</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eff7247decd592d</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad58dde8c86078b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics and Visualization</t>
+          <t>Senior Full Stack Developer - Java</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Also</t>
+          <t>Simplain Software Solutions LLC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Walnut, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Databricks, Spark</t>
+          <t>S3, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe62c0aa52bf9aa</t>
+          <t>https://www.indeed.com/viewjob?jk=0eff7247decd592d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python &amp; Snowflake)</t>
+          <t>Senior Data Engineer - Analytics and Visualization</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>3Pillar Global</t>
+          <t>Also</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Snowflake, SQL Server, DynamoDB, dbt</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff80065b4fd4799</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe62c0aa52bf9aa</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Senior Data Engineer (Python &amp; Snowflake)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>3Pillar Global</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Snowflake, SQL Server, DynamoDB, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d21a5637c26aeee6</t>
+          <t>https://www.indeed.com/viewjob?jk=bff80065b4fd4799</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18d46da9a88bc799</t>
+          <t>https://www.indeed.com/viewjob?jk=d21a5637c26aeee6</t>
         </is>
       </c>
     </row>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28ea1b73fd02e910</t>
+          <t>https://www.indeed.com/viewjob?jk=18d46da9a88bc799</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520267b51ab833b5</t>
+          <t>https://www.indeed.com/viewjob?jk=28ea1b73fd02e910</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77901b3684582750</t>
+          <t>https://www.indeed.com/viewjob?jk=520267b51ab833b5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Cloud - Platform Test</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4d5281c97057bc</t>
+          <t>https://www.indeed.com/viewjob?jk=77901b3684582750</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DEVELOPER L3</t>
+          <t>Sr. Software Engineer, Cloud - Platform Test</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>North Quincy, MA, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72c2c42a5838eae6</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4d5281c97057bc</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, MarTech</t>
+          <t>DEVELOPER L3</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>North Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1daebb30fd5fc85c</t>
+          <t>https://www.indeed.com/viewjob?jk=72c2c42a5838eae6</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SDET</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc49399df060bfe1</t>
+          <t>https://www.indeed.com/viewjob?jk=f7e36064fcccf83f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>.NET Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>TraXtion</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7e36064fcccf83f</t>
+          <t>https://www.indeed.com/viewjob?jk=24f809df752b708e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>.NET Software Engineer</t>
+          <t>SDET</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>TraXtion</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Scala, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f809df752b708e</t>
+          <t>https://www.indeed.com/viewjob?jk=bc49399df060bfe1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Developer III - Application Development</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>LightEdge</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f3984b03cd26c72</t>
+          <t>https://www.indeed.com/viewjob?jk=7bb7334f3f2d66e8</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LightEdge</t>
+          <t>RJW Logistics</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bb7334f3f2d66e8</t>
+          <t>https://www.indeed.com/viewjob?jk=00950f1140481fca</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Developer III - Application Development</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>RJW Logistics</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,17 +2516,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00950f1140481fca</t>
+          <t>https://www.indeed.com/viewjob?jk=4f3984b03cd26c72</t>
         </is>
       </c>
     </row>
@@ -2708,17 +2708,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Software Development Engineer II - ML Platform</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Waséyabek Development Company</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Otsego, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Azure, Kafka, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=467fe0059b658cf7</t>
+          <t>https://www.indeed.com/viewjob?jk=6f38667e23fc2e6a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - ML Platform</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Waséyabek Development Company</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Otsego, MI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Kubernetes</t>
+          <t>Azure, Kafka, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f38667e23fc2e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=467fe0059b658cf7</t>
         </is>
       </c>
     </row>
@@ -3198,17 +3198,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud - Test Platform</t>
+          <t>Senior Engineer -.NET</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, Cassandra, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=089cf1934f4cd6a4</t>
+          <t>https://www.indeed.com/viewjob?jk=a13dd69a11dd2a2a</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Enterprise Data Analytics and AI Developer</t>
+          <t>Sr. Engineer, Cloud - Test Platform</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Dudek</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
+          <t>AWS, S3, RDS, Scala, Kafka, Cassandra, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,19 +3261,19 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d343da250ebc576a</t>
+          <t>https://www.indeed.com/viewjob?jk=089cf1934f4cd6a4</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Enterprise Data Analytics and AI Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GreenBox Capital</t>
+          <t>Dudek</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83d3f50fcc4de14e</t>
+          <t>https://www.indeed.com/viewjob?jk=d343da250ebc576a</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>GreenBox Capital</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,19 +3331,19 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d27208e71b125f4</t>
+          <t>https://www.indeed.com/viewjob?jk=83d3f50fcc4de14e</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f423abaf086a5787</t>
+          <t>https://www.indeed.com/viewjob?jk=2d27208e71b125f4</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d37428d214fe7e4f</t>
+          <t>https://www.indeed.com/viewjob?jk=f423abaf086a5787</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Developer III - Application Development (Data Integration)</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,15 +3426,50 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d37428d214fe7e4f</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Developer III - Application Development (Data Integration)</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Inland Empire Health Plan</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Rancho Cucamonga, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
           <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>2025-09-24</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ee815ea22a573add</t>
         </is>

--- a/results/job_matches_2026-03-25.xlsx
+++ b/results/job_matches_2026-03-25.xlsx
@@ -713,25 +713,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kiely Family of Companies</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tinton Falls, NJ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8ac6e29a223b095</t>
+          <t>https://www.indeed.com/viewjob?jk=933ad44aa47970a9</t>
         </is>
       </c>
     </row>
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b2ba9ffb9a799d</t>
+          <t>https://www.indeed.com/viewjob?jk=a8ac6e29a223b095</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Kiely Family of Companies</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tinton Falls, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d2d9cf01e65cfd8</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b2ba9ffb9a799d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,42 +836,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cec5fe386ea9e81</t>
+          <t>https://www.indeed.com/viewjob?jk=0d2d9cf01e65cfd8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2fd5678c94e0e11</t>
+          <t>https://www.indeed.com/viewjob?jk=1cec5fe386ea9e81</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Salesforce Service Cloud Specialist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c63d8ea7f769e54</t>
+          <t>https://www.indeed.com/viewjob?jk=d2fd5678c94e0e11</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Salesforce Service Cloud Specialist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Live Nation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, API Gateway, RDS, Databricks, Scala, SQL Server</t>
+          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2d1e17a962b5fca</t>
+          <t>https://www.indeed.com/viewjob?jk=8c63d8ea7f769e54</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Live Nation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, API Gateway, RDS, Databricks, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15957719609ec59</t>
+          <t>https://www.indeed.com/viewjob?jk=d2d1e17a962b5fca</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Foundations Engineer</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73966b170bd92bef</t>
+          <t>https://www.indeed.com/viewjob?jk=d15957719609ec59</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f328d78d7b80a9bf</t>
+          <t>https://www.indeed.com/viewjob?jk=73966b170bd92bef</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19cd66b829b5339a</t>
+          <t>https://www.indeed.com/viewjob?jk=f328d78d7b80a9bf</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a15946806730eb5d</t>
+          <t>https://www.indeed.com/viewjob?jk=19cd66b829b5339a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Foundations Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Old National Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lake Elmo, MN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1ae7b8f4932aea6</t>
+          <t>https://www.indeed.com/viewjob?jk=a15946806730eb5d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Augment Professional Services</t>
+          <t>Old National Bank</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Lake Elmo, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e76e474f9e2efb6</t>
+          <t>https://www.indeed.com/viewjob?jk=f1ae7b8f4932aea6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Augment Professional Services</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, RDS, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70b82e4ad32cd227</t>
+          <t>https://www.indeed.com/viewjob?jk=4e76e474f9e2efb6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IT Data Engineer - Level 3</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cintas</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, Spark</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2550c832064daf74</t>
+          <t>https://www.indeed.com/viewjob?jk=70b82e4ad32cd227</t>
         </is>
       </c>
     </row>
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35633737b3f1427c</t>
+          <t>https://www.indeed.com/viewjob?jk=2550c832064daf74</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>IT Data Engineer - Level 3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cintas</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5ed7b4a07ec36ef</t>
+          <t>https://www.indeed.com/viewjob?jk=35633737b3f1427c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Hadoop, Spark, PySpark, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cec7ac1f3411b653</t>
+          <t>https://www.indeed.com/viewjob?jk=e5ed7b4a07ec36ef</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect + Security Czar</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>hr@brxio.com</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Hadoop, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Hadoop, Spark, PySpark, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9cfc8c1e5c32169</t>
+          <t>https://www.indeed.com/viewjob?jk=cec7ac1f3411b653</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr Data Scientist</t>
+          <t>Data Warehouse Architect + Security Czar</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>hr@brxio.com</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Hadoop, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad58dde8c86078b</t>
+          <t>https://www.indeed.com/viewjob?jk=a9cfc8c1e5c32169</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - Java</t>
+          <t>Sr Data Scientist</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Simplain Software Solutions LLC</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Walnut, CA, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, Power BI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eff7247decd592d</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad58dde8c86078b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics and Visualization</t>
+          <t>Senior Full Stack Developer - Java</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Also</t>
+          <t>Simplain Software Solutions LLC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Walnut, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Databricks, Spark</t>
+          <t>S3, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe62c0aa52bf9aa</t>
+          <t>https://www.indeed.com/viewjob?jk=0eff7247decd592d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python &amp; Snowflake)</t>
+          <t>Senior Data Engineer - Analytics and Visualization</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>3Pillar Global</t>
+          <t>Also</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Snowflake, SQL Server, DynamoDB, dbt</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff80065b4fd4799</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe62c0aa52bf9aa</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Senior Data Engineer (Python &amp; Snowflake)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>3Pillar Global</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Snowflake, SQL Server, DynamoDB, dbt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d21a5637c26aeee6</t>
+          <t>https://www.indeed.com/viewjob?jk=bff80065b4fd4799</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18d46da9a88bc799</t>
+          <t>https://www.indeed.com/viewjob?jk=d21a5637c26aeee6</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28ea1b73fd02e910</t>
+          <t>https://www.indeed.com/viewjob?jk=18d46da9a88bc799</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520267b51ab833b5</t>
+          <t>https://www.indeed.com/viewjob?jk=28ea1b73fd02e910</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77901b3684582750</t>
+          <t>https://www.indeed.com/viewjob?jk=520267b51ab833b5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Cloud - Platform Test</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4d5281c97057bc</t>
+          <t>https://www.indeed.com/viewjob?jk=77901b3684582750</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DEVELOPER L3</t>
+          <t>Sr. Software Engineer, Cloud - Platform Test</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>North Quincy, MA, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72c2c42a5838eae6</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4d5281c97057bc</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DEVELOPER L3</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Intellias</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>North Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c59056599f6669cd</t>
+          <t>https://www.indeed.com/viewjob?jk=72c2c42a5838eae6</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>IT AI&amp;S Senior Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>Intellias</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd7ea95be40f976</t>
+          <t>https://www.indeed.com/viewjob?jk=c59056599f6669cd</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>IT AI&amp;S Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ClickBank</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, RDS, Scala, MySQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=412f3333e8a582ca</t>
+          <t>https://www.indeed.com/viewjob?jk=9dd7ea95be40f976</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>IT AI&amp;S Senior Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>ClickBank</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, S3, SQS, SNS, IAM, RDS, Scala, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e29bb5eef54aab18</t>
+          <t>https://www.indeed.com/viewjob?jk=412f3333e8a582ca</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
+          <t>IT AI&amp;S Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Oxford Economics</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d76d14c5568ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=e29bb5eef54aab18</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CD Excellence Data Engineering Associate</t>
+          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Unilever</t>
+          <t>Oxford Economics</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c49b3555427c9f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d76d14c5568ea6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
+          <t>CD Excellence Data Engineering Associate</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Oxford Economics</t>
+          <t>Unilever</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1782e281cbd34a</t>
+          <t>https://www.indeed.com/viewjob?jk=c49b3555427c9f7a</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Oxford Economics</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=983aa41d463e2b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1782e281cbd34a</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>The Shade Store</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80c249f67538f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=983aa41d463e2b8e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Intellias</t>
+          <t>The Shade Store</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc90240b32e9d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=c80c249f67538f2f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Database Engineer with Java MS</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Intellias</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,59 +2176,59 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b94269754a9820</t>
+          <t>https://www.indeed.com/viewjob?jk=5fc90240b32e9d4a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Database Engineer with Java MS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, ECS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=103595c75d73a7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=25b94269754a9820</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Intern - Cloud Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, Scala, Kafka, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f194b7e973e71ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=103595c75d73a7c1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Intern - Cloud Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mercari</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, Scala, Kafka, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69b773db1c488113</t>
+          <t>https://www.indeed.com/viewjob?jk=f194b7e973e71ef2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Mercari</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fa1c79d7085ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=69b773db1c488113</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7e36064fcccf83f</t>
+          <t>https://www.indeed.com/viewjob?jk=65fa1c79d7085ebe</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>.NET Software Engineer</t>
+          <t>SDET</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>TraXtion</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Scala, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f809df752b708e</t>
+          <t>https://www.indeed.com/viewjob?jk=bc49399df060bfe1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SDET</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc49399df060bfe1</t>
+          <t>https://www.indeed.com/viewjob?jk=f7e36064fcccf83f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>.NET Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>LightEdge</t>
+          <t>TraXtion</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bb7334f3f2d66e8</t>
+          <t>https://www.indeed.com/viewjob?jk=24f809df752b708e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>RJW Logistics</t>
+          <t>LightEdge</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,17 +2481,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00950f1140481fca</t>
+          <t>https://www.indeed.com/viewjob?jk=7bb7334f3f2d66e8</t>
         </is>
       </c>
     </row>
@@ -2708,17 +2708,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - ML Platform</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Waséyabek Development Company</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Otsego, MI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Kubernetes</t>
+          <t>Azure, Kafka, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f38667e23fc2e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=467fe0059b658cf7</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Software Development Engineer II - ML Platform</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Waséyabek Development Company</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Otsego, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Azure, Kafka, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=467fe0059b658cf7</t>
+          <t>https://www.indeed.com/viewjob?jk=6f38667e23fc2e6a</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-25.xlsx
+++ b/results/job_matches_2026-03-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III: DevOps</t>
+          <t>Cloud Data Platform Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, Scala</t>
+          <t>Google Cloud Platform, GCP, Dataflow, Cloud Storage, Spark, Scala, Snowflake, NoSQL, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed96ac951faf1fe</t>
+          <t>https://www.indeed.com/viewjob?jk=815d21355bca9afb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Engineer</t>
+          <t>Devops - Embedded Engineer - IOT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Brillius</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Dataflow, Cloud Storage, Spark, Scala, Snowflake, NoSQL, Data Modeling, Kimball</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,59 +636,59 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=815d21355bca9afb</t>
+          <t>https://www.indeed.com/viewjob?jk=7e14322c45e210aa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Devops - Embedded Engineer - IOT</t>
+          <t>Python and PySpark, No SQL Developer-1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Brillius</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, DynamoDB</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e14322c45e210aa</t>
+          <t>https://www.indeed.com/viewjob?jk=934a100fa2f03442</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Python and PySpark, No SQL Developer-1</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=934a100fa2f03442</t>
+          <t>https://www.indeed.com/viewjob?jk=933ad44aa47970a9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Kiely Family of Companies</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Tinton Falls, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog, Spark</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=933ad44aa47970a9</t>
+          <t>https://www.indeed.com/viewjob?jk=a8ac6e29a223b095</t>
         </is>
       </c>
     </row>
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8ac6e29a223b095</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b2ba9ffb9a799d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kiely Family of Companies</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tinton Falls, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b2ba9ffb9a799d</t>
+          <t>https://www.indeed.com/viewjob?jk=0d2d9cf01e65cfd8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,42 +836,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d2d9cf01e65cfd8</t>
+          <t>https://www.indeed.com/viewjob?jk=1cec5fe386ea9e81</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cec5fe386ea9e81</t>
+          <t>https://www.indeed.com/viewjob?jk=d2fd5678c94e0e11</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Salesforce Service Cloud Specialist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2fd5678c94e0e11</t>
+          <t>https://www.indeed.com/viewjob?jk=8c63d8ea7f769e54</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Salesforce Service Cloud Specialist</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Live Nation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, API Gateway, RDS, Databricks, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c63d8ea7f769e54</t>
+          <t>https://www.indeed.com/viewjob?jk=d2d1e17a962b5fca</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Live Nation</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, API Gateway, RDS, Databricks, Scala, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2d1e17a962b5fca</t>
+          <t>https://www.indeed.com/viewjob?jk=d15957719609ec59</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Data Foundations Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15957719609ec59</t>
+          <t>https://www.indeed.com/viewjob?jk=73966b170bd92bef</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73966b170bd92bef</t>
+          <t>https://www.indeed.com/viewjob?jk=f328d78d7b80a9bf</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f328d78d7b80a9bf</t>
+          <t>https://www.indeed.com/viewjob?jk=19cd66b829b5339a</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19cd66b829b5339a</t>
+          <t>https://www.indeed.com/viewjob?jk=a15946806730eb5d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Foundations Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Old National Bank</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Lake Elmo, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a15946806730eb5d</t>
+          <t>https://www.indeed.com/viewjob?jk=f1ae7b8f4932aea6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Old National Bank</t>
+          <t>Augment Professional Services</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lake Elmo, MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, RDS, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1ae7b8f4932aea6</t>
+          <t>https://www.indeed.com/viewjob?jk=4e76e474f9e2efb6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Augment Professional Services</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e76e474f9e2efb6</t>
+          <t>https://www.indeed.com/viewjob?jk=70b82e4ad32cd227</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>IT Data Engineer - Level 3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Cintas</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70b82e4ad32cd227</t>
+          <t>https://www.indeed.com/viewjob?jk=2550c832064daf74</t>
         </is>
       </c>
     </row>
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2550c832064daf74</t>
+          <t>https://www.indeed.com/viewjob?jk=35633737b3f1427c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IT Data Engineer - Level 3</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cintas</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, Spark</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35633737b3f1427c</t>
+          <t>https://www.indeed.com/viewjob?jk=e5ed7b4a07ec36ef</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Hadoop, Spark, PySpark, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5ed7b4a07ec36ef</t>
+          <t>https://www.indeed.com/viewjob?jk=cec7ac1f3411b653</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer - Analytics and Visualization</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>Also</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Hadoop, Spark, PySpark, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cec7ac1f3411b653</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe62c0aa52bf9aa</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect + Security Czar</t>
+          <t>Senior Full Stack Developer - Java</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>hr@brxio.com</t>
+          <t>Simplain Software Solutions LLC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Walnut, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Hadoop, Spark, Scala, Oracle, SQL Server</t>
+          <t>S3, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9cfc8c1e5c32169</t>
+          <t>https://www.indeed.com/viewjob?jk=0eff7247decd592d</t>
         </is>
       </c>
     </row>
@@ -1483,25 +1483,25 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - Java</t>
+          <t>Senior Data Engineer (Python &amp; Snowflake)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Simplain Software Solutions LLC</t>
+          <t>3Pillar Global</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Walnut, CA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Snowflake, SQL Server, DynamoDB, dbt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eff7247decd592d</t>
+          <t>https://www.indeed.com/viewjob?jk=bff80065b4fd4799</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics and Visualization</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Also</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Databricks, Spark</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe62c0aa52bf9aa</t>
+          <t>https://www.indeed.com/viewjob?jk=d21a5637c26aeee6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python &amp; Snowflake)</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>3Pillar Global</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Snowflake, SQL Server, DynamoDB, dbt</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff80065b4fd4799</t>
+          <t>https://www.indeed.com/viewjob?jk=18d46da9a88bc799</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d21a5637c26aeee6</t>
+          <t>https://www.indeed.com/viewjob?jk=28ea1b73fd02e910</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18d46da9a88bc799</t>
+          <t>https://www.indeed.com/viewjob?jk=520267b51ab833b5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28ea1b73fd02e910</t>
+          <t>https://www.indeed.com/viewjob?jk=77901b3684582750</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Sr. Software Engineer, Cloud - Platform Test</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520267b51ab833b5</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4d5281c97057bc</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>DEVELOPER L3</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>North Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77901b3684582750</t>
+          <t>https://www.indeed.com/viewjob?jk=72c2c42a5838eae6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Cloud - Platform Test</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Intellias</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Jenkins</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4d5281c97057bc</t>
+          <t>https://www.indeed.com/viewjob?jk=c59056599f6669cd</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DEVELOPER L3</t>
+          <t>AI Product Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>North Quincy, MA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72c2c42a5838eae6</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef1d9dc4f2a3c77</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>IT AI&amp;S Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Intellias</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c59056599f6669cd</t>
+          <t>https://www.indeed.com/viewjob?jk=9dd7ea95be40f976</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>IT AI&amp;S Senior Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>ClickBank</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, S3, SQS, SNS, IAM, RDS, Scala, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd7ea95be40f976</t>
+          <t>https://www.indeed.com/viewjob?jk=412f3333e8a582ca</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>IT AI&amp;S Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ClickBank</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, RDS, Scala, MySQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=412f3333e8a582ca</t>
+          <t>https://www.indeed.com/viewjob?jk=e29bb5eef54aab18</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>IT AI&amp;S Senior Data Engineer</t>
+          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>Oxford Economics</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e29bb5eef54aab18</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d76d14c5568ea6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
+          <t>CD Excellence Data Engineering Associate</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Oxford Economics</t>
+          <t>Unilever</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d76d14c5568ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=c49b3555427c9f7a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CD Excellence Data Engineering Associate</t>
+          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Unilever</t>
+          <t>Oxford Economics</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c49b3555427c9f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1782e281cbd34a</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Oxford Economics</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1782e281cbd34a</t>
+          <t>https://www.indeed.com/viewjob?jk=983aa41d463e2b8e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>The Shade Store</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=983aa41d463e2b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=c80c249f67538f2f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>The Shade Store</t>
+          <t>Intellias</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80c249f67538f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=5fc90240b32e9d4a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Database Engineer with Java MS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Intellias</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, ECS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,59 +2176,59 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc90240b32e9d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=25b94269754a9820</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Database Engineer with Java MS</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b94269754a9820</t>
+          <t>https://www.indeed.com/viewjob?jk=103595c75d73a7c1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Intern - Cloud Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, Scala, Kafka, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=103595c75d73a7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=f194b7e973e71ef2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Intern - Cloud Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Mercari</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, Scala, Kafka, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f194b7e973e71ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=69b773db1c488113</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Mercari</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
+          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69b773db1c488113</t>
+          <t>https://www.indeed.com/viewjob?jk=65fa1c79d7085ebe</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>SDET</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Scala, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fa1c79d7085ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=bc49399df060bfe1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SDET</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>LightEdge</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc49399df060bfe1</t>
+          <t>https://www.indeed.com/viewjob?jk=7bb7334f3f2d66e8</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Developer III - Application Development</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,139 +2411,139 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7e36064fcccf83f</t>
+          <t>https://www.indeed.com/viewjob?jk=4f3984b03cd26c72</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>.NET Software Engineer</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>TraXtion</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Owings Mills, MD, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f809df752b708e</t>
+          <t>https://www.indeed.com/viewjob?jk=4b8eb10a2720f342</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LightEdge</t>
+          <t>MOHELA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Azure, Hive, Impala, Spark, Scala, Data Modeling, ETL, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bb7334f3f2d66e8</t>
+          <t>https://www.indeed.com/viewjob?jk=00ea21484fff4c0b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Developer III - Application Development</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
+          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f3984b03cd26c72</t>
+          <t>https://www.indeed.com/viewjob?jk=6767c0e89ecdbcae</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Distinguished Architect, Data Platform</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Owings Mills, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,19 +2561,19 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b8eb10a2720f342</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd1095da2d18982</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Software Development Engineer II - ML Platform</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6767c0e89ecdbcae</t>
+          <t>https://www.indeed.com/viewjob?jk=6f38667e23fc2e6a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GM Motorsports</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e18d9eef9566cc88</t>
+          <t>https://www.indeed.com/viewjob?jk=c873a7854b5a7a4a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Distinguished Architect, Data Platform</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>Waséyabek Development Company</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Otsego, MI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
+          <t>Azure, Kafka, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd1095da2d18982</t>
+          <t>https://www.indeed.com/viewjob?jk=467fe0059b658cf7</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Plante Moran</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>El Dorado Hills, CA, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c873a7854b5a7a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=39cd370d20d11526</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Waséyabek Development Company</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Otsego, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Azure, Kafka, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=467fe0059b658cf7</t>
+          <t>https://www.indeed.com/viewjob?jk=1074f4222424a549</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - ML Platform</t>
+          <t>Software Engineer - Full Stack (EAA - Compliance)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, MongoDB, NoSQL, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f38667e23fc2e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=4577a3ce998c3da0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Plante Moran</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, CI/CD, GitHub Actions</t>
+          <t>Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39cd370d20d11526</t>
+          <t>https://www.indeed.com/viewjob?jk=4c10749649c748ef</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Full Stack Developer Intern</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Westford, MA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,67 +2841,67 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1074f4222424a549</t>
+          <t>https://www.indeed.com/viewjob?jk=e6d07eb218f7af80</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack (EAA - Compliance)</t>
+          <t>Senior Quality Platform Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Circle.so</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, MongoDB, NoSQL, ETL, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4577a3ce998c3da0</t>
+          <t>https://www.indeed.com/viewjob?jk=235baa8877534de1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Burlington Stores</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Edgewater Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c10749649c748ef</t>
+          <t>https://www.indeed.com/viewjob?jk=d93e23fa17175252</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Full Stack Developer Intern</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fanatics</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Westford, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Kinesis, Redshift, S3, RDS, Kafka, MongoDB, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6d07eb218f7af80</t>
+          <t>https://www.indeed.com/viewjob?jk=5daf9a09c12e8d35</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Quality Platform Engineer</t>
+          <t>Experienced Data &amp; AI Platform Cloud DevOps / DataOps Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Circle.so</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Blob Storage, Unity Catalog, Scala, DataOps, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=235baa8877534de1</t>
+          <t>https://www.indeed.com/viewjob?jk=1cbeb2be8c0c0a59</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Burlington Stores</t>
+          <t>The Clearing House Payments Company</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Edgewater Park, NJ, US USA</t>
+          <t>Liberty, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Kinesis, Scala, Kafka, Tableau, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d93e23fa17175252</t>
+          <t>https://www.indeed.com/viewjob?jk=beb95949bff9aca2</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Engineer -.NET</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Fanatics</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, RDS, Kafka, MongoDB, Tableau, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5daf9a09c12e8d35</t>
+          <t>https://www.indeed.com/viewjob?jk=a13dd69a11dd2a2a</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Experienced Data &amp; AI Platform Cloud DevOps / DataOps Engineer</t>
+          <t>Enterprise Data Analytics and AI Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Dudek</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Blob Storage, Unity Catalog, Scala, DataOps, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cbeb2be8c0c0a59</t>
+          <t>https://www.indeed.com/viewjob?jk=d343da250ebc576a</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>The Clearing House Payments Company</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Liberty, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Scala, Kafka, Tableau, CI/CD, Terraform, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beb95949bff9aca2</t>
+          <t>https://www.indeed.com/viewjob?jk=7da3735857b8f1b1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Engineer IV, Data Engineering</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Omnicell</t>
+          <t>GreenBox Capital</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Python, SQL</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46ffdeefe4f68e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=83d3f50fcc4de14e</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7da3735857b8f1b1</t>
+          <t>https://www.indeed.com/viewjob?jk=2d27208e71b125f4</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Engineer -.NET</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a13dd69a11dd2a2a</t>
+          <t>https://www.indeed.com/viewjob?jk=d37428d214fe7e4f</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud - Test Platform</t>
+          <t>Engineer IV, Data Engineering</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Omnicell</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, Cassandra, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=089cf1934f4cd6a4</t>
+          <t>https://www.indeed.com/viewjob?jk=46ffdeefe4f68e9e</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Enterprise Data Analytics and AI Developer</t>
+          <t>Developer III - Application Development (Data Integration)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Dudek</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,190 +3286,15 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
+          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d343da250ebc576a</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>GreenBox Capital</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=83d3f50fcc4de14e</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2d27208e71b125f4</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Senior Java Developer</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Conduent</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f423abaf086a5787</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Engineer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d37428d214fe7e4f</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Developer III - Application Development (Data Integration)</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Inland Empire Health Plan</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ee815ea22a573add</t>
         </is>

--- a/results/job_matches_2026-03-25.xlsx
+++ b/results/job_matches_2026-03-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -993,25 +993,25 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Foundations Engineer</t>
+          <t>Engineer, Storage Engineering</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, Scala, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73966b170bd92bef</t>
+          <t>https://www.indeed.com/viewjob?jk=f47fe1b011621142</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f328d78d7b80a9bf</t>
+          <t>https://www.indeed.com/viewjob?jk=73966b170bd92bef</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19cd66b829b5339a</t>
+          <t>https://www.indeed.com/viewjob?jk=f328d78d7b80a9bf</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a15946806730eb5d</t>
+          <t>https://www.indeed.com/viewjob?jk=19cd66b829b5339a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Foundations Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Old National Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lake Elmo, MN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1ae7b8f4932aea6</t>
+          <t>https://www.indeed.com/viewjob?jk=a15946806730eb5d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Augment Professional Services</t>
+          <t>Old National Bank</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Lake Elmo, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e76e474f9e2efb6</t>
+          <t>https://www.indeed.com/viewjob?jk=f1ae7b8f4932aea6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Augment Professional Services</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, RDS, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70b82e4ad32cd227</t>
+          <t>https://www.indeed.com/viewjob?jk=4e76e474f9e2efb6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IT Data Engineer - Level 3</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cintas</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, Spark</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2550c832064daf74</t>
+          <t>https://www.indeed.com/viewjob?jk=70b82e4ad32cd227</t>
         </is>
       </c>
     </row>
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35633737b3f1427c</t>
+          <t>https://www.indeed.com/viewjob?jk=2550c832064daf74</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>IT Data Engineer - Level 3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cintas</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5ed7b4a07ec36ef</t>
+          <t>https://www.indeed.com/viewjob?jk=35633737b3f1427c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Hadoop, Spark, PySpark, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cec7ac1f3411b653</t>
+          <t>https://www.indeed.com/viewjob?jk=e5ed7b4a07ec36ef</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics and Visualization</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Also</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Databricks, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Hadoop, Spark, PySpark, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe62c0aa52bf9aa</t>
+          <t>https://www.indeed.com/viewjob?jk=cec7ac1f3411b653</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - Java</t>
+          <t>Senior Data Engineer - Analytics and Visualization</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Simplain Software Solutions LLC</t>
+          <t>Also</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Walnut, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eff7247decd592d</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe62c0aa52bf9aa</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr Data Scientist</t>
+          <t>Senior Full Stack Developer - Java</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Simplain Software Solutions LLC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Walnut, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,69 +1466,69 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, Power BI</t>
+          <t>S3, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad58dde8c86078b</t>
+          <t>https://www.indeed.com/viewjob?jk=0eff7247decd592d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python &amp; Snowflake)</t>
+          <t>Sr Data Scientist</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>3Pillar Global</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Snowflake, SQL Server, DynamoDB, dbt</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff80065b4fd4799</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad58dde8c86078b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>Azure, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d21a5637c26aeee6</t>
+          <t>https://www.indeed.com/viewjob?jk=799dc2ba53bfb669</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Senior Data Engineer (Python &amp; Snowflake)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>3Pillar Global</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Snowflake, SQL Server, DynamoDB, dbt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18d46da9a88bc799</t>
+          <t>https://www.indeed.com/viewjob?jk=bff80065b4fd4799</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Fusion Academy</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Scala, Kafka, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28ea1b73fd02e910</t>
+          <t>https://www.indeed.com/viewjob?jk=c239fde5950cdb3c</t>
         </is>
       </c>
     </row>
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520267b51ab833b5</t>
+          <t>https://www.indeed.com/viewjob?jk=d21a5637c26aeee6</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77901b3684582750</t>
+          <t>https://www.indeed.com/viewjob?jk=18d46da9a88bc799</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Cloud - Platform Test</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Jenkins</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4d5281c97057bc</t>
+          <t>https://www.indeed.com/viewjob?jk=28ea1b73fd02e910</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DEVELOPER L3</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>North Quincy, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72c2c42a5838eae6</t>
+          <t>https://www.indeed.com/viewjob?jk=520267b51ab833b5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Intellias</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c59056599f6669cd</t>
+          <t>https://www.indeed.com/viewjob?jk=77901b3684582750</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI Product Engineer</t>
+          <t>Sr. Software Engineer, Cloud - Platform Test</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, ELT, dbt, MLOps</t>
+          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef1d9dc4f2a3c77</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4d5281c97057bc</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>IT AI&amp;S Senior Data Engineer</t>
+          <t>DEVELOPER L3</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>North Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd7ea95be40f976</t>
+          <t>https://www.indeed.com/viewjob?jk=72c2c42a5838eae6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ClickBank</t>
+          <t>Intellias</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, RDS, Scala, MySQL, DynamoDB, CI/CD</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=412f3333e8a582ca</t>
+          <t>https://www.indeed.com/viewjob?jk=c59056599f6669cd</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>IT AI&amp;S Senior Data Engineer</t>
+          <t>AI Product Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e29bb5eef54aab18</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef1d9dc4f2a3c77</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
+          <t>IT AI&amp;S Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Oxford Economics</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d76d14c5568ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=9dd7ea95be40f976</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CD Excellence Data Engineering Associate</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Unilever</t>
+          <t>ClickBank</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, SQS, SNS, IAM, RDS, Scala, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c49b3555427c9f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=412f3333e8a582ca</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
+          <t>IT AI&amp;S Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Oxford Economics</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1782e281cbd34a</t>
+          <t>https://www.indeed.com/viewjob?jk=e29bb5eef54aab18</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Oxford Economics</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=983aa41d463e2b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d76d14c5568ea6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>CD Excellence Data Engineering Associate</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>The Shade Store</t>
+          <t>Unilever</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80c249f67538f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=c49b3555427c9f7a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Intellias</t>
+          <t>Oxford Economics</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc90240b32e9d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1782e281cbd34a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Database Engineer with Java MS</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,77 +2166,77 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b94269754a9820</t>
+          <t>https://www.indeed.com/viewjob?jk=983aa41d463e2b8e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>The Shade Store</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=103595c75d73a7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=c80c249f67538f2f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Intern - Cloud Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Intellias</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, Scala, Kafka, DynamoDB, NoSQL</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f194b7e973e71ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=5fc90240b32e9d4a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Database Engineer with Java MS</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mercari</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
+          <t>AWS, ECS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69b773db1c488113</t>
+          <t>https://www.indeed.com/viewjob?jk=25b94269754a9820</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fa1c79d7085ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=103595c75d73a7c1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SDET</t>
+          <t>Intern - Cloud Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, Scala, Kafka, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc49399df060bfe1</t>
+          <t>https://www.indeed.com/viewjob?jk=f194b7e973e71ef2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>LightEdge</t>
+          <t>Mercari</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bb7334f3f2d66e8</t>
+          <t>https://www.indeed.com/viewjob?jk=69b773db1c488113</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Developer III - Application Development</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,42 +2411,42 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f3984b03cd26c72</t>
+          <t>https://www.indeed.com/viewjob?jk=65fa1c79d7085ebe</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>SDET</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Owings Mills, MD, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
+          <t>RDS, Azure, Scala, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,94 +2456,94 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b8eb10a2720f342</t>
+          <t>https://www.indeed.com/viewjob?jk=bc49399df060bfe1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MOHELA</t>
+          <t>LightEdge</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hive, Impala, Spark, Scala, Data Modeling, ETL, Azure DevOps, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00ea21484fff4c0b</t>
+          <t>https://www.indeed.com/viewjob?jk=7bb7334f3f2d66e8</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Developer III - Application Development</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6767c0e89ecdbcae</t>
+          <t>https://www.indeed.com/viewjob?jk=4f3984b03cd26c72</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Distinguished Architect, Data Platform</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Owings Mills, MD, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd1095da2d18982</t>
+          <t>https://www.indeed.com/viewjob?jk=4b8eb10a2720f342</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - ML Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>MOHELA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Kubernetes</t>
+          <t>RDS, Azure, Hive, Impala, Spark, Scala, Data Modeling, ETL, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f38667e23fc2e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=00ea21484fff4c0b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>El Dorado Hills, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
+          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c873a7854b5a7a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=6767c0e89ecdbcae</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Distinguished Architect, Data Platform</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Waséyabek Development Company</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Otsego, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Azure, Kafka, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=467fe0059b658cf7</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd1095da2d18982</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Plante Moran</t>
+          <t>Waséyabek Development Company</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Otsego, MI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, CI/CD, GitHub Actions</t>
+          <t>Azure, Kafka, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39cd370d20d11526</t>
+          <t>https://www.indeed.com/viewjob?jk=467fe0059b658cf7</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Software Development Engineer II - ML Platform</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Docker</t>
+          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1074f4222424a549</t>
+          <t>https://www.indeed.com/viewjob?jk=6f38667e23fc2e6a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack (EAA - Compliance)</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, MongoDB, NoSQL, ETL, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4577a3ce998c3da0</t>
+          <t>https://www.indeed.com/viewjob?jk=c873a7854b5a7a4a</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Plante Moran</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c10749649c748ef</t>
+          <t>https://www.indeed.com/viewjob?jk=39cd370d20d11526</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Full Stack Developer Intern</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Westford, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
+          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,67 +2841,67 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6d07eb218f7af80</t>
+          <t>https://www.indeed.com/viewjob?jk=1074f4222424a549</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Quality Platform Engineer</t>
+          <t>Software Engineer - Full Stack (EAA - Compliance)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Circle.so</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, MongoDB, NoSQL, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=235baa8877534de1</t>
+          <t>https://www.indeed.com/viewjob?jk=4577a3ce998c3da0</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Burlington Stores</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Edgewater Park, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
+          <t>Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d93e23fa17175252</t>
+          <t>https://www.indeed.com/viewjob?jk=4c10749649c748ef</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Full Stack Developer Intern</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Fanatics</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Westford, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, RDS, Kafka, MongoDB, Tableau, CI/CD, Airflow</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5daf9a09c12e8d35</t>
+          <t>https://www.indeed.com/viewjob?jk=e6d07eb218f7af80</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Experienced Data &amp; AI Platform Cloud DevOps / DataOps Engineer</t>
+          <t>Senior Quality Platform Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Circle.so</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Blob Storage, Unity Catalog, Scala, DataOps, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cbeb2be8c0c0a59</t>
+          <t>https://www.indeed.com/viewjob?jk=235baa8877534de1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>The Clearing House Payments Company</t>
+          <t>Burlington Stores</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Liberty, NY, US USA</t>
+          <t>Edgewater Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Scala, Kafka, Tableau, CI/CD, Terraform, Git, Python</t>
+          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beb95949bff9aca2</t>
+          <t>https://www.indeed.com/viewjob?jk=d93e23fa17175252</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Engineer -.NET</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Fanatics</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, Redshift, S3, RDS, Kafka, MongoDB, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a13dd69a11dd2a2a</t>
+          <t>https://www.indeed.com/viewjob?jk=5daf9a09c12e8d35</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Enterprise Data Analytics and AI Developer</t>
+          <t>Experienced Data &amp; AI Platform Cloud DevOps / DataOps Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Dudek</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
+          <t>RDS, Azure, Databricks, Blob Storage, Unity Catalog, Scala, DataOps, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d343da250ebc576a</t>
+          <t>https://www.indeed.com/viewjob?jk=1cbeb2be8c0c0a59</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>The Clearing House Payments Company</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Liberty, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, Glue, Kinesis, Scala, Kafka, Tableau, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7da3735857b8f1b1</t>
+          <t>https://www.indeed.com/viewjob?jk=beb95949bff9aca2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Engineer -.NET</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GreenBox Capital</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83d3f50fcc4de14e</t>
+          <t>https://www.indeed.com/viewjob?jk=a13dd69a11dd2a2a</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Enterprise Data Analytics and AI Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Dudek</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d27208e71b125f4</t>
+          <t>https://www.indeed.com/viewjob?jk=d343da250ebc576a</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d37428d214fe7e4f</t>
+          <t>https://www.indeed.com/viewjob?jk=7da3735857b8f1b1</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Engineer IV, Data Engineering</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Omnicell</t>
+          <t>GreenBox Capital</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Python, SQL</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46ffdeefe4f68e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=83d3f50fcc4de14e</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Developer III - Application Development (Data Integration)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,15 +3286,120 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d27208e71b125f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Engineer IV, Data Engineering</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Omnicell</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46ffdeefe4f68e9e</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d37428d214fe7e4f</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Developer III - Application Development (Data Integration)</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Inland Empire Health Plan</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Rancho Cucamonga, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
           <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>2025-09-24</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ee815ea22a573add</t>
         </is>

--- a/results/job_matches_2026-03-25.xlsx
+++ b/results/job_matches_2026-03-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2673,17 +2673,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Software Development Engineer II - ML Platform</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Waséyabek Development Company</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Otsego, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Azure, Kafka, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=467fe0059b658cf7</t>
+          <t>https://www.indeed.com/viewjob?jk=6f38667e23fc2e6a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - ML Platform</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f38667e23fc2e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=c873a7854b5a7a4a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Waséyabek Development Company</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>El Dorado Hills, CA, US USA</t>
+          <t>Otsego, MI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
+          <t>Azure, Kafka, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c873a7854b5a7a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=467fe0059b658cf7</t>
         </is>
       </c>
     </row>
@@ -2918,25 +2918,25 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Full Stack Developer Intern</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Gong</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Westford, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
+          <t>AWS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6d07eb218f7af80</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb90cff4906f695</t>
         </is>
       </c>
     </row>
@@ -3268,17 +3268,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d27208e71b125f4</t>
+          <t>https://www.indeed.com/viewjob?jk=d37428d214fe7e4f</t>
         </is>
       </c>
     </row>
@@ -3338,17 +3338,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Developer III - Application Development (Data Integration)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,50 +3356,15 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d37428d214fe7e4f</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Developer III - Application Development (Data Integration)</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Inland Empire Health Plan</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ee815ea22a573add</t>
         </is>

--- a/results/job_matches_2026-03-25.xlsx
+++ b/results/job_matches_2026-03-25.xlsx
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Live Nation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, API Gateway, RDS, Databricks, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2fd5678c94e0e11</t>
+          <t>https://www.indeed.com/viewjob?jk=d2d1e17a962b5fca</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Salesforce Service Cloud Specialist</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c63d8ea7f769e54</t>
+          <t>https://www.indeed.com/viewjob?jk=d15957719609ec59</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Live Nation</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, API Gateway, RDS, Databricks, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2d1e17a962b5fca</t>
+          <t>https://www.indeed.com/viewjob?jk=d2fd5678c94e0e11</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Salesforce Service Cloud Specialist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15957719609ec59</t>
+          <t>https://www.indeed.com/viewjob?jk=8c63d8ea7f769e54</t>
         </is>
       </c>
     </row>
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>IT Data Engineer - Level 3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Cintas</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70b82e4ad32cd227</t>
+          <t>https://www.indeed.com/viewjob?jk=2550c832064daf74</t>
         </is>
       </c>
     </row>
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2550c832064daf74</t>
+          <t>https://www.indeed.com/viewjob?jk=35633737b3f1427c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IT Data Engineer - Level 3</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cintas</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, Spark</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35633737b3f1427c</t>
+          <t>https://www.indeed.com/viewjob?jk=e5ed7b4a07ec36ef</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Hadoop, Spark, PySpark, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5ed7b4a07ec36ef</t>
+          <t>https://www.indeed.com/viewjob?jk=cec7ac1f3411b653</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Hadoop, Spark, PySpark, SQL Server, Data Modeling</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cec7ac1f3411b653</t>
+          <t>https://www.indeed.com/viewjob?jk=70b82e4ad32cd227</t>
         </is>
       </c>
     </row>
@@ -1518,17 +1518,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Fusion Academy</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Scala, Kafka, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=799dc2ba53bfb669</t>
+          <t>https://www.indeed.com/viewjob?jk=c239fde5950cdb3c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python &amp; Snowflake)</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>3Pillar Global</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Snowflake, SQL Server, DynamoDB, dbt</t>
+          <t>Azure, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff80065b4fd4799</t>
+          <t>https://www.indeed.com/viewjob?jk=799dc2ba53bfb669</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fusion Academy</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Scala, Kafka, Data Modeling, ELT</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c239fde5950cdb3c</t>
+          <t>https://www.indeed.com/viewjob?jk=d21a5637c26aeee6</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d21a5637c26aeee6</t>
+          <t>https://www.indeed.com/viewjob?jk=18d46da9a88bc799</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18d46da9a88bc799</t>
+          <t>https://www.indeed.com/viewjob?jk=28ea1b73fd02e910</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28ea1b73fd02e910</t>
+          <t>https://www.indeed.com/viewjob?jk=520267b51ab833b5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520267b51ab833b5</t>
+          <t>https://www.indeed.com/viewjob?jk=77901b3684582750</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Data Engineer (Python &amp; Snowflake)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>3Pillar Global</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Snowflake, SQL Server, DynamoDB, dbt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77901b3684582750</t>
+          <t>https://www.indeed.com/viewjob?jk=bff80065b4fd4799</t>
         </is>
       </c>
     </row>
@@ -1868,17 +1868,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Product Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Intellias</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c59056599f6669cd</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef1d9dc4f2a3c77</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Product Engineer</t>
+          <t>IT AI&amp;S Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, ELT, dbt, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef1d9dc4f2a3c77</t>
+          <t>https://www.indeed.com/viewjob?jk=9dd7ea95be40f976</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>IT AI&amp;S Senior Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>ClickBank</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, S3, SQS, SNS, IAM, RDS, Scala, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd7ea95be40f976</t>
+          <t>https://www.indeed.com/viewjob?jk=412f3333e8a582ca</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>IT AI&amp;S Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ClickBank</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, RDS, Scala, MySQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=412f3333e8a582ca</t>
+          <t>https://www.indeed.com/viewjob?jk=e29bb5eef54aab18</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>IT AI&amp;S Senior Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>Intellias</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e29bb5eef54aab18</t>
+          <t>https://www.indeed.com/viewjob?jk=c59056599f6669cd</t>
         </is>
       </c>
     </row>
@@ -2113,17 +2113,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Oxford Economics</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1782e281cbd34a</t>
+          <t>https://www.indeed.com/viewjob?jk=983aa41d463e2b8e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>The Shade Store</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=983aa41d463e2b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=c80c249f67538f2f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The Shade Store</t>
+          <t>Intellias</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80c249f67538f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=5fc90240b32e9d4a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Database Engineer with Java MS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Intellias</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, ECS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,59 +2246,59 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc90240b32e9d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=25b94269754a9820</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Database Engineer with Java MS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Expertshub</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b94269754a9820</t>
+          <t>https://www.indeed.com/viewjob?jk=74923e4619f29cbd</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Intern - Cloud Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, Scala, Kafka, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=103595c75d73a7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=f194b7e973e71ef2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Intern - Cloud Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,17 +2341,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, Scala, Kafka, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f194b7e973e71ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=103595c75d73a7c1</t>
         </is>
       </c>
     </row>
@@ -2568,17 +2568,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MOHELA</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hive, Impala, Spark, Scala, Data Modeling, ETL, Azure DevOps, Airflow</t>
+          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00ea21484fff4c0b</t>
+          <t>https://www.indeed.com/viewjob?jk=6767c0e89ecdbcae</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>MOHELA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Hive, Impala, Spark, Scala, Data Modeling, ETL, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6767c0e89ecdbcae</t>
+          <t>https://www.indeed.com/viewjob?jk=00ea21484fff4c0b</t>
         </is>
       </c>
     </row>
@@ -2918,17 +2918,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Gong</t>
+          <t>Burlington Stores</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Edgewater Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb90cff4906f695</t>
+          <t>https://www.indeed.com/viewjob?jk=d93e23fa17175252</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Quality Platform Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Circle.so</t>
+          <t>Fanatics</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>AWS, Kinesis, Redshift, S3, RDS, Kafka, MongoDB, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=235baa8877534de1</t>
+          <t>https://www.indeed.com/viewjob?jk=5daf9a09c12e8d35</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Experienced Data &amp; AI Platform Cloud DevOps / DataOps Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Burlington Stores</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Edgewater Park, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Databricks, Blob Storage, Unity Catalog, Scala, DataOps, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d93e23fa17175252</t>
+          <t>https://www.indeed.com/viewjob?jk=1cbeb2be8c0c0a59</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Fanatics</t>
+          <t>The Clearing House Payments Company</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Liberty, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, RDS, Kafka, MongoDB, Tableau, CI/CD, Airflow</t>
+          <t>AWS, Glue, Kinesis, Scala, Kafka, Tableau, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5daf9a09c12e8d35</t>
+          <t>https://www.indeed.com/viewjob?jk=beb95949bff9aca2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Experienced Data &amp; AI Platform Cloud DevOps / DataOps Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Gong</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Blob Storage, Unity Catalog, Scala, DataOps, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cbeb2be8c0c0a59</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb90cff4906f695</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Quality Platform Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>The Clearing House Payments Company</t>
+          <t>Circle.so</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Liberty, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,17 +3111,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Scala, Kafka, Tableau, CI/CD, Terraform, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beb95949bff9aca2</t>
+          <t>https://www.indeed.com/viewjob?jk=235baa8877534de1</t>
         </is>
       </c>
     </row>
@@ -3268,17 +3268,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Engineer IV, Data Engineering</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Omnicell</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d37428d214fe7e4f</t>
+          <t>https://www.indeed.com/viewjob?jk=46ffdeefe4f68e9e</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Engineer IV, Data Engineering</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Omnicell</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Python, SQL</t>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46ffdeefe4f68e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=d37428d214fe7e4f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-25.xlsx
+++ b/results/job_matches_2026-03-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,95 +538,95 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior BackEnd Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, ECS, IAM, RDS</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69b516454f937a66</t>
+          <t>https://www.indeed.com/viewjob?jk=b5da0b19b9bea7fb</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Dataflow, Cloud Storage, Spark, Scala, Snowflake, NoSQL, Data Modeling, Kimball</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=815d21355bca9afb</t>
+          <t>https://www.indeed.com/viewjob?jk=69b516454f937a66</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Devops - Embedded Engineer - IOT</t>
+          <t>Cloud Data Platform Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Brillius</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, DynamoDB</t>
+          <t>Google Cloud Platform, GCP, Dataflow, Cloud Storage, Spark, Scala, Snowflake, NoSQL, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,59 +636,59 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e14322c45e210aa</t>
+          <t>https://www.indeed.com/viewjob?jk=815d21355bca9afb</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Python and PySpark, No SQL Developer-1</t>
+          <t>Devops - Embedded Engineer - IOT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Brillius</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=934a100fa2f03442</t>
+          <t>https://www.indeed.com/viewjob?jk=7e14322c45e210aa</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Python and PySpark, No SQL Developer-1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog, Spark</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=933ad44aa47970a9</t>
+          <t>https://www.indeed.com/viewjob?jk=934a100fa2f03442</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kiely Family of Companies</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tinton Falls, NJ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8ac6e29a223b095</t>
+          <t>https://www.indeed.com/viewjob?jk=933ad44aa47970a9</t>
         </is>
       </c>
     </row>
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b2ba9ffb9a799d</t>
+          <t>https://www.indeed.com/viewjob?jk=a8ac6e29a223b095</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Kiely Family of Companies</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tinton Falls, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d2d9cf01e65cfd8</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b2ba9ffb9a799d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,42 +836,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cec5fe386ea9e81</t>
+          <t>https://www.indeed.com/viewjob?jk=0d2d9cf01e65cfd8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Live Nation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, API Gateway, RDS, Databricks, Scala, SQL Server</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2d1e17a962b5fca</t>
+          <t>https://www.indeed.com/viewjob?jk=1cec5fe386ea9e81</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15957719609ec59</t>
+          <t>https://www.indeed.com/viewjob?jk=d2fd5678c94e0e11</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Salesforce Service Cloud Specialist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2fd5678c94e0e11</t>
+          <t>https://www.indeed.com/viewjob?jk=8c63d8ea7f769e54</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Salesforce Service Cloud Specialist</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Live Nation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, API Gateway, RDS, Databricks, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c63d8ea7f769e54</t>
+          <t>https://www.indeed.com/viewjob?jk=d2d1e17a962b5fca</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Engineer, Storage Engineering</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, Scala, Tableau, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f47fe1b011621142</t>
+          <t>https://www.indeed.com/viewjob?jk=d15957719609ec59</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Foundations Engineer</t>
+          <t>Engineer, Storage Engineering</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, Scala, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73966b170bd92bef</t>
+          <t>https://www.indeed.com/viewjob?jk=f47fe1b011621142</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f328d78d7b80a9bf</t>
+          <t>https://www.indeed.com/viewjob?jk=73966b170bd92bef</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19cd66b829b5339a</t>
+          <t>https://www.indeed.com/viewjob?jk=f328d78d7b80a9bf</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a15946806730eb5d</t>
+          <t>https://www.indeed.com/viewjob?jk=19cd66b829b5339a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Foundations Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Old National Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lake Elmo, MN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1ae7b8f4932aea6</t>
+          <t>https://www.indeed.com/viewjob?jk=a15946806730eb5d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Augment Professional Services</t>
+          <t>Old National Bank</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Lake Elmo, MN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e76e474f9e2efb6</t>
+          <t>https://www.indeed.com/viewjob?jk=f1ae7b8f4932aea6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IT Data Engineer - Level 3</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cintas</t>
+          <t>Augment Professional Services</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, Spark</t>
+          <t>AWS, Lambda, RDS, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2550c832064daf74</t>
+          <t>https://www.indeed.com/viewjob?jk=4e76e474f9e2efb6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IT Data Engineer - Level 3</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cintas</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, Spark</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35633737b3f1427c</t>
+          <t>https://www.indeed.com/viewjob?jk=70b82e4ad32cd227</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>IT Data Engineer - Level 3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cintas</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5ed7b4a07ec36ef</t>
+          <t>https://www.indeed.com/viewjob?jk=2550c832064daf74</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>IT Data Engineer - Level 3</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>Cintas</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Hadoop, Spark, PySpark, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cec7ac1f3411b653</t>
+          <t>https://www.indeed.com/viewjob?jk=35633737b3f1427c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70b82e4ad32cd227</t>
+          <t>https://www.indeed.com/viewjob?jk=6a60f5615bdba859</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics and Visualization</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Also</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Databricks, Spark</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe62c0aa52bf9aa</t>
+          <t>https://www.indeed.com/viewjob?jk=e5ed7b4a07ec36ef</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - Java</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Simplain Software Solutions LLC</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Walnut, CA, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Hadoop, Spark, PySpark, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eff7247decd592d</t>
+          <t>https://www.indeed.com/viewjob?jk=cec7ac1f3411b653</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr Data Scientist</t>
+          <t>Senior Data Engineer - Analytics and Visualization</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Also</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,77 +1501,77 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, Power BI</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad58dde8c86078b</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe62c0aa52bf9aa</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack Developer - Java</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fusion Academy</t>
+          <t>Simplain Software Solutions LLC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Walnut, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Scala, Kafka, Data Modeling, ELT</t>
+          <t>S3, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c239fde5950cdb3c</t>
+          <t>https://www.indeed.com/viewjob?jk=0eff7247decd592d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Sr Data Scientist</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Azure, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Oracle, SQL Server, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=799dc2ba53bfb669</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad58dde8c86078b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>Azure, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d21a5637c26aeee6</t>
+          <t>https://www.indeed.com/viewjob?jk=799dc2ba53bfb669</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Fusion Academy</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Scala, Kafka, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18d46da9a88bc799</t>
+          <t>https://www.indeed.com/viewjob?jk=c239fde5950cdb3c</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28ea1b73fd02e910</t>
+          <t>https://www.indeed.com/viewjob?jk=d21a5637c26aeee6</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520267b51ab833b5</t>
+          <t>https://www.indeed.com/viewjob?jk=18d46da9a88bc799</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77901b3684582750</t>
+          <t>https://www.indeed.com/viewjob?jk=28ea1b73fd02e910</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python &amp; Snowflake)</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>3Pillar Global</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Snowflake, SQL Server, DynamoDB, dbt</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff80065b4fd4799</t>
+          <t>https://www.indeed.com/viewjob?jk=520267b51ab833b5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Cloud - Platform Test</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4d5281c97057bc</t>
+          <t>https://www.indeed.com/viewjob?jk=77901b3684582750</t>
         </is>
       </c>
     </row>
@@ -1868,25 +1868,25 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Product Engineer</t>
+          <t>Sr. Software Engineer, Cloud - Platform Test</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, ELT, dbt, MLOps</t>
+          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef1d9dc4f2a3c77</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4d5281c97057bc</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>IT AI&amp;S Senior Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>Intellias</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd7ea95be40f976</t>
+          <t>https://www.indeed.com/viewjob?jk=c59056599f6669cd</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>AI Product Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ClickBank</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, RDS, Scala, MySQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=412f3333e8a582ca</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef1d9dc4f2a3c77</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e29bb5eef54aab18</t>
+          <t>https://www.indeed.com/viewjob?jk=9dd7ea95be40f976</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Intellias</t>
+          <t>ClickBank</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, S3, SQS, SNS, IAM, RDS, Scala, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c59056599f6669cd</t>
+          <t>https://www.indeed.com/viewjob?jk=412f3333e8a582ca</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
+          <t>IT AI&amp;S Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Oxford Economics</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d76d14c5568ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=e29bb5eef54aab18</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CD Excellence Data Engineering Associate</t>
+          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Unilever</t>
+          <t>Oxford Economics</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c49b3555427c9f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d76d14c5568ea6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>CD Excellence Data Engineering Associate</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Unilever</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=983aa41d463e2b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=c49b3555427c9f7a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>The Shade Store</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80c249f67538f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=983aa41d463e2b8e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Intellias</t>
+          <t>The Shade Store</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc90240b32e9d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=c80c249f67538f2f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Database Engineer with Java MS</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Intellias</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,54 +2246,54 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b94269754a9820</t>
+          <t>https://www.indeed.com/viewjob?jk=5fc90240b32e9d4a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Database Engineer with Java MS</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Expertshub</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, ECS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74923e4619f29cbd</t>
+          <t>https://www.indeed.com/viewjob?jk=25b94269754a9820</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Intern - Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Expertshub</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2306,17 +2306,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, Scala, Kafka, DynamoDB, NoSQL</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f194b7e973e71ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=74923e4619f29cbd</t>
         </is>
       </c>
     </row>
@@ -2358,17 +2358,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Intern - Cloud Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Mercari</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, Scala, Kafka, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69b773db1c488113</t>
+          <t>https://www.indeed.com/viewjob?jk=f194b7e973e71ef2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Mercari</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fa1c79d7085ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=69b773db1c488113</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SDET</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc49399df060bfe1</t>
+          <t>https://www.indeed.com/viewjob?jk=65fa1c79d7085ebe</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Developer III - Application Development</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LightEdge</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bb7334f3f2d66e8</t>
+          <t>https://www.indeed.com/viewjob?jk=4f3984b03cd26c72</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Developer III - Application Development</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>LightEdge</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,42 +2516,42 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f3984b03cd26c72</t>
+          <t>https://www.indeed.com/viewjob?jk=7bb7334f3f2d66e8</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>SDET</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Owings Mills, MD, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
+          <t>RDS, Azure, Scala, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b8eb10a2720f342</t>
+          <t>https://www.indeed.com/viewjob?jk=bc49399df060bfe1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Owings Mills, MD, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6767c0e89ecdbcae</t>
+          <t>https://www.indeed.com/viewjob?jk=4b8eb10a2720f342</t>
         </is>
       </c>
     </row>
@@ -2638,17 +2638,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Distinguished Architect, Data Platform</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd1095da2d18982</t>
+          <t>https://www.indeed.com/viewjob?jk=6767c0e89ecdbcae</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - ML Platform</t>
+          <t>Distinguished Architect, Data Platform</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Kubernetes</t>
+          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f38667e23fc2e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd1095da2d18982</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Software Development Engineer II - ML Platform</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>El Dorado Hills, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
+          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c873a7854b5a7a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=6f38667e23fc2e6a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Waséyabek Development Company</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Otsego, MI, US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Azure, Kafka, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=467fe0059b658cf7</t>
+          <t>https://www.indeed.com/viewjob?jk=c873a7854b5a7a4a</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Plante Moran</t>
+          <t>Waséyabek Development Company</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Otsego, MI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, CI/CD, GitHub Actions</t>
+          <t>Azure, Kafka, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39cd370d20d11526</t>
+          <t>https://www.indeed.com/viewjob?jk=467fe0059b658cf7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Plante Moran</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Docker</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1074f4222424a549</t>
+          <t>https://www.indeed.com/viewjob?jk=39cd370d20d11526</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack (EAA - Compliance)</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, MongoDB, NoSQL, ETL, Terraform, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4577a3ce998c3da0</t>
+          <t>https://www.indeed.com/viewjob?jk=1074f4222424a549</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Software Engineer - Full Stack (EAA - Compliance)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,42 +2901,42 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, MongoDB, NoSQL, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c10749649c748ef</t>
+          <t>https://www.indeed.com/viewjob?jk=4577a3ce998c3da0</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Burlington Stores</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Edgewater Park, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
+          <t>Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d93e23fa17175252</t>
+          <t>https://www.indeed.com/viewjob?jk=4c10749649c748ef</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Fanatics</t>
+          <t>Gong</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, RDS, Kafka, MongoDB, Tableau, CI/CD, Airflow</t>
+          <t>AWS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5daf9a09c12e8d35</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb90cff4906f695</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Experienced Data &amp; AI Platform Cloud DevOps / DataOps Engineer</t>
+          <t>Senior Quality Platform Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Circle.so</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Blob Storage, Unity Catalog, Scala, DataOps, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cbeb2be8c0c0a59</t>
+          <t>https://www.indeed.com/viewjob?jk=235baa8877534de1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>The Clearing House Payments Company</t>
+          <t>Burlington Stores</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Liberty, NY, US USA</t>
+          <t>Edgewater Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Scala, Kafka, Tableau, CI/CD, Terraform, Git, Python</t>
+          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beb95949bff9aca2</t>
+          <t>https://www.indeed.com/viewjob?jk=d93e23fa17175252</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Gong</t>
+          <t>Fanatics</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Kinesis, Redshift, S3, RDS, Kafka, MongoDB, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb90cff4906f695</t>
+          <t>https://www.indeed.com/viewjob?jk=5daf9a09c12e8d35</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Quality Platform Engineer</t>
+          <t>Experienced Data &amp; AI Platform Cloud DevOps / DataOps Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Circle.so</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Blob Storage, Unity Catalog, Scala, DataOps, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=235baa8877534de1</t>
+          <t>https://www.indeed.com/viewjob?jk=1cbeb2be8c0c0a59</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Engineer -.NET</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>The Clearing House Payments Company</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Liberty, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, Kinesis, Scala, Kafka, Tableau, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a13dd69a11dd2a2a</t>
+          <t>https://www.indeed.com/viewjob?jk=beb95949bff9aca2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Enterprise Data Analytics and AI Developer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Dudek</t>
+          <t>Polaris I/O</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, DynamoDB, Data Modeling, ELT, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d343da250ebc576a</t>
+          <t>https://www.indeed.com/viewjob?jk=f266e67ee961e84e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Engineer -.NET</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,29 +3216,29 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7da3735857b8f1b1</t>
+          <t>https://www.indeed.com/viewjob?jk=a13dd69a11dd2a2a</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Enterprise Data Analytics and AI Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GreenBox Capital</t>
+          <t>Dudek</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83d3f50fcc4de14e</t>
+          <t>https://www.indeed.com/viewjob?jk=d343da250ebc576a</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Engineer IV, Data Engineering</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Omnicell</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Python, SQL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46ffdeefe4f68e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=7da3735857b8f1b1</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>GreenBox Capital</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d37428d214fe7e4f</t>
+          <t>https://www.indeed.com/viewjob?jk=83d3f50fcc4de14e</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Developer III - Application Development (Data Integration)</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,17 +3356,87 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d37428d214fe7e4f</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Developer III - Application Development (Data Integration)</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Inland Empire Health Plan</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Rancho Cucamonga, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
           <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>2025-09-24</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ee815ea22a573add</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Engineer IV, Data Engineering</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Omnicell</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46ffdeefe4f68e9e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-25.xlsx
+++ b/results/job_matches_2026-03-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Azure, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Oracle, SQL Server, ETL</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=799dc2ba53bfb669</t>
+          <t>https://www.indeed.com/viewjob?jk=073969ba933b74ce</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fusion Academy</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Scala, Kafka, Data Modeling, ELT</t>
+          <t>Azure, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c239fde5950cdb3c</t>
+          <t>https://www.indeed.com/viewjob?jk=799dc2ba53bfb669</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Fusion Academy</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Scala, Kafka, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d21a5637c26aeee6</t>
+          <t>https://www.indeed.com/viewjob?jk=c239fde5950cdb3c</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18d46da9a88bc799</t>
+          <t>https://www.indeed.com/viewjob?jk=d21a5637c26aeee6</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28ea1b73fd02e910</t>
+          <t>https://www.indeed.com/viewjob?jk=18d46da9a88bc799</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520267b51ab833b5</t>
+          <t>https://www.indeed.com/viewjob?jk=28ea1b73fd02e910</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77901b3684582750</t>
+          <t>https://www.indeed.com/viewjob?jk=520267b51ab833b5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DEVELOPER L3</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>North Quincy, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72c2c42a5838eae6</t>
+          <t>https://www.indeed.com/viewjob?jk=77901b3684582750</t>
         </is>
       </c>
     </row>
@@ -1903,12 +1903,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Engineer, MarTech</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Intellias</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1917,11 +1917,11 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c59056599f6669cd</t>
+          <t>https://www.indeed.com/viewjob?jk=1daebb30fd5fc85c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Product Engineer</t>
+          <t>DEVELOPER L3</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>North Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, ELT, dbt, MLOps</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef1d9dc4f2a3c77</t>
+          <t>https://www.indeed.com/viewjob?jk=72c2c42a5838eae6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>IT AI&amp;S Senior Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>Intellias</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd7ea95be40f976</t>
+          <t>https://www.indeed.com/viewjob?jk=c59056599f6669cd</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>AI Product Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ClickBank</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, RDS, Scala, MySQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=412f3333e8a582ca</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef1d9dc4f2a3c77</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e29bb5eef54aab18</t>
+          <t>https://www.indeed.com/viewjob?jk=9dd7ea95be40f976</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Oxford Economics</t>
+          <t>ClickBank</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
+          <t>AWS, S3, SQS, SNS, IAM, RDS, Scala, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d76d14c5568ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=412f3333e8a582ca</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CD Excellence Data Engineering Associate</t>
+          <t>IT AI&amp;S Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Unilever</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c49b3555427c9f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=e29bb5eef54aab18</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Oxford Economics</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=983aa41d463e2b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d76d14c5568ea6</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The Shade Store</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80c249f67538f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=983aa41d463e2b8e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Intellias</t>
+          <t>The Shade Store</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc90240b32e9d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=c80c249f67538f2f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Database Engineer with Java MS</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Intellias</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,42 +2281,42 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b94269754a9820</t>
+          <t>https://www.indeed.com/viewjob?jk=5fc90240b32e9d4a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Database Engineer with Java MS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Expertshub</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, ECS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74923e4619f29cbd</t>
+          <t>https://www.indeed.com/viewjob?jk=25b94269754a9820</t>
         </is>
       </c>
     </row>
@@ -2393,17 +2393,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Senior Software Engineer - Hadoop Infrastructure</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Mercari</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
+          <t>RDS, Hadoop, HDFS, Hive, HBase, Oozie, YARN, Spark, Scala, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69b773db1c488113</t>
+          <t>https://www.indeed.com/viewjob?jk=57aca64828ae44c2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr Java Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Futrend Technology, Inc</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
+          <t>AWS, S3, RDS, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fa1c79d7085ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=66e658594e26e266</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Developer III - Application Development</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>Mercari</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f3984b03cd26c72</t>
+          <t>https://www.indeed.com/viewjob?jk=69b773db1c488113</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LightEdge</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bb7334f3f2d66e8</t>
+          <t>https://www.indeed.com/viewjob?jk=65fa1c79d7085ebe</t>
         </is>
       </c>
     </row>
@@ -2568,25 +2568,25 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>LightEdge</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Owings Mills, MD, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,59 +2596,59 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b8eb10a2720f342</t>
+          <t>https://www.indeed.com/viewjob?jk=7bb7334f3f2d66e8</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Developer III - Application Development</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MOHELA</t>
+          <t>Inland Empire Health Plan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rancho Cucamonga, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hive, Impala, Spark, Scala, Data Modeling, ETL, Azure DevOps, Airflow</t>
+          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00ea21484fff4c0b</t>
+          <t>https://www.indeed.com/viewjob?jk=4f3984b03cd26c72</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Owings Mills, MD, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6767c0e89ecdbcae</t>
+          <t>https://www.indeed.com/viewjob?jk=4b8eb10a2720f342</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Distinguished Architect, Data Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>MOHELA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
+          <t>RDS, Azure, Hive, Impala, Spark, Scala, Data Modeling, ETL, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd1095da2d18982</t>
+          <t>https://www.indeed.com/viewjob?jk=00ea21484fff4c0b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - ML Platform</t>
+          <t>Database Administrator / Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Clear Channel Outdoor</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Kubernetes</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, SQL Server, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f38667e23fc2e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=1e24a399eaddada3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>El Dorado Hills, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
+          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c873a7854b5a7a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=6767c0e89ecdbcae</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Distinguished Architect, Data Platform</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Waséyabek Development Company</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Otsego, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Azure, Kafka, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=467fe0059b658cf7</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd1095da2d18982</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Software Development Engineer II - ML Platform</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Plante Moran</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39cd370d20d11526</t>
+          <t>https://www.indeed.com/viewjob?jk=6f38667e23fc2e6a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1074f4222424a549</t>
+          <t>https://www.indeed.com/viewjob?jk=c873a7854b5a7a4a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack (EAA - Compliance)</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Waséyabek Development Company</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Otsego, MI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, MongoDB, NoSQL, ETL, Terraform, Kubernetes</t>
+          <t>Azure, Kafka, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4577a3ce998c3da0</t>
+          <t>https://www.indeed.com/viewjob?jk=467fe0059b658cf7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Plante Moran</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c10749649c748ef</t>
+          <t>https://www.indeed.com/viewjob?jk=39cd370d20d11526</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Gong</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,67 +2981,67 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb90cff4906f695</t>
+          <t>https://www.indeed.com/viewjob?jk=1074f4222424a549</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Quality Platform Engineer</t>
+          <t>Software Engineer - Full Stack (EAA - Compliance)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Circle.so</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, MongoDB, NoSQL, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=235baa8877534de1</t>
+          <t>https://www.indeed.com/viewjob?jk=4577a3ce998c3da0</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Burlington Stores</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Edgewater Park, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
+          <t>Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d93e23fa17175252</t>
+          <t>https://www.indeed.com/viewjob?jk=4c10749649c748ef</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Quality Platform Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Fanatics</t>
+          <t>Circle.so</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, RDS, Kafka, MongoDB, Tableau, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5daf9a09c12e8d35</t>
+          <t>https://www.indeed.com/viewjob?jk=235baa8877534de1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Experienced Data &amp; AI Platform Cloud DevOps / DataOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Burlington Stores</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Edgewater Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Blob Storage, Unity Catalog, Scala, DataOps, CI/CD, Jenkins, Terraform</t>
+          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cbeb2be8c0c0a59</t>
+          <t>https://www.indeed.com/viewjob?jk=d93e23fa17175252</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>The Clearing House Payments Company</t>
+          <t>Fanatics</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Liberty, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Scala, Kafka, Tableau, CI/CD, Terraform, Git, Python</t>
+          <t>AWS, Kinesis, Redshift, S3, RDS, Kafka, MongoDB, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beb95949bff9aca2</t>
+          <t>https://www.indeed.com/viewjob?jk=5daf9a09c12e8d35</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Experienced Data &amp; AI Platform Cloud DevOps / DataOps Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Polaris I/O</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, DynamoDB, Data Modeling, ELT, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Blob Storage, Unity Catalog, Scala, DataOps, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f266e67ee961e84e</t>
+          <t>https://www.indeed.com/viewjob?jk=1cbeb2be8c0c0a59</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Engineer -.NET</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>The Clearing House Payments Company</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Liberty, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, Kinesis, Scala, Kafka, Tableau, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a13dd69a11dd2a2a</t>
+          <t>https://www.indeed.com/viewjob?jk=beb95949bff9aca2</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Enterprise Data Analytics and AI Developer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Dudek</t>
+          <t>Polaris I/O</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, DynamoDB, Data Modeling, ELT, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d343da250ebc576a</t>
+          <t>https://www.indeed.com/viewjob?jk=f266e67ee961e84e</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Engineer -.NET</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,29 +3286,29 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7da3735857b8f1b1</t>
+          <t>https://www.indeed.com/viewjob?jk=a13dd69a11dd2a2a</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Enterprise Data Analytics and AI Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GreenBox Capital</t>
+          <t>Dudek</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83d3f50fcc4de14e</t>
+          <t>https://www.indeed.com/viewjob?jk=d343da250ebc576a</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d37428d214fe7e4f</t>
+          <t>https://www.indeed.com/viewjob?jk=7da3735857b8f1b1</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Developer III - Application Development (Data Integration)</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>GreenBox Capital</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,17 +3391,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee815ea22a573add</t>
+          <t>https://www.indeed.com/viewjob?jk=83d3f50fcc4de14e</t>
         </is>
       </c>
     </row>
@@ -3437,6 +3437,76 @@
       <c r="G86" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=46ffdeefe4f68e9e</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d37428d214fe7e4f</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Developer III - Application Development (Data Integration)</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Inland Empire Health Plan</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Rancho Cucamonga, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee815ea22a573add</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-25.xlsx
+++ b/results/job_matches_2026-03-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Dataflow, Cloud Storage, Spark, Scala, Snowflake, NoSQL, Data Modeling, Kimball</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=815d21355bca9afb</t>
+          <t>https://www.indeed.com/viewjob?jk=8ae0639bcc380726</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Devops - Embedded Engineer - IOT</t>
+          <t>Cloud Data Platform Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Brillius</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, DynamoDB</t>
+          <t>Google Cloud Platform, GCP, Dataflow, Cloud Storage, Spark, Scala, Snowflake, NoSQL, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e14322c45e210aa</t>
+          <t>https://www.indeed.com/viewjob?jk=815d21355bca9afb</t>
         </is>
       </c>
     </row>
@@ -1028,25 +1028,25 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Engineer, Storage Engineering</t>
+          <t>Data Foundations Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Cloud Storage, Scala, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f47fe1b011621142</t>
+          <t>https://www.indeed.com/viewjob?jk=73966b170bd92bef</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73966b170bd92bef</t>
+          <t>https://www.indeed.com/viewjob?jk=f328d78d7b80a9bf</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f328d78d7b80a9bf</t>
+          <t>https://www.indeed.com/viewjob?jk=19cd66b829b5339a</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19cd66b829b5339a</t>
+          <t>https://www.indeed.com/viewjob?jk=a15946806730eb5d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Foundations Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Old National Bank</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Lake Elmo, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a15946806730eb5d</t>
+          <t>https://www.indeed.com/viewjob?jk=f1ae7b8f4932aea6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Old National Bank</t>
+          <t>Augment Professional Services</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lake Elmo, MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, RDS, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1ae7b8f4932aea6</t>
+          <t>https://www.indeed.com/viewjob?jk=4e76e474f9e2efb6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Augment Professional Services</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e76e474f9e2efb6</t>
+          <t>https://www.indeed.com/viewjob?jk=70b82e4ad32cd227</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>IT Data Engineer - Level 3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Cintas</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70b82e4ad32cd227</t>
+          <t>https://www.indeed.com/viewjob?jk=2550c832064daf74</t>
         </is>
       </c>
     </row>
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2550c832064daf74</t>
+          <t>https://www.indeed.com/viewjob?jk=35633737b3f1427c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IT Data Engineer - Level 3</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cintas</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, Spark</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35633737b3f1427c</t>
+          <t>https://www.indeed.com/viewjob?jk=6a60f5615bdba859</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a60f5615bdba859</t>
+          <t>https://www.indeed.com/viewjob?jk=e5ed7b4a07ec36ef</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Senior Data Engineer - Analytics and Visualization</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Also</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5ed7b4a07ec36ef</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe62c0aa52bf9aa</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Full Stack Developer - Java</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>Simplain Software Solutions LLC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Walnut, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Hadoop, Spark, PySpark, SQL Server, Data Modeling</t>
+          <t>S3, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cec7ac1f3411b653</t>
+          <t>https://www.indeed.com/viewjob?jk=0eff7247decd592d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics and Visualization</t>
+          <t>Sr Data Scientist</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Also</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,77 +1501,77 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Databricks, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe62c0aa52bf9aa</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad58dde8c86078b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - Java</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Simplain Software Solutions LLC</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Walnut, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eff7247decd592d</t>
+          <t>https://www.indeed.com/viewjob?jk=1b263e0344e64430</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr Data Scientist</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, Power BI</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad58dde8c86078b</t>
+          <t>https://www.indeed.com/viewjob?jk=073969ba933b74ce</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark</t>
+          <t>Azure, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=073969ba933b74ce</t>
+          <t>https://www.indeed.com/viewjob?jk=799dc2ba53bfb669</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Fusion Academy</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Scala, Kafka, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=799dc2ba53bfb669</t>
+          <t>https://www.indeed.com/viewjob?jk=c239fde5950cdb3c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fusion Academy</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Scala, Kafka, Data Modeling, ELT</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c239fde5950cdb3c</t>
+          <t>https://www.indeed.com/viewjob?jk=d21a5637c26aeee6</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d21a5637c26aeee6</t>
+          <t>https://www.indeed.com/viewjob?jk=18d46da9a88bc799</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18d46da9a88bc799</t>
+          <t>https://www.indeed.com/viewjob?jk=28ea1b73fd02e910</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28ea1b73fd02e910</t>
+          <t>https://www.indeed.com/viewjob?jk=520267b51ab833b5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520267b51ab833b5</t>
+          <t>https://www.indeed.com/viewjob?jk=77901b3684582750</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Sr. Software Engineer, Cloud - Platform Test</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77901b3684582750</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4d5281c97057bc</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Cloud - Platform Test</t>
+          <t>Senior AI Engineer, MarTech</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4d5281c97057bc</t>
+          <t>https://www.indeed.com/viewjob?jk=1daebb30fd5fc85c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, MarTech</t>
+          <t>DEVELOPER L3</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>North Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1daebb30fd5fc85c</t>
+          <t>https://www.indeed.com/viewjob?jk=72c2c42a5838eae6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DEVELOPER L3</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Intellias</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>North Quincy, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72c2c42a5838eae6</t>
+          <t>https://www.indeed.com/viewjob?jk=c59056599f6669cd</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Product Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Intellias</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c59056599f6669cd</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef1d9dc4f2a3c77</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI Product Engineer</t>
+          <t>IT AI&amp;S Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, ELT, dbt, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef1d9dc4f2a3c77</t>
+          <t>https://www.indeed.com/viewjob?jk=9dd7ea95be40f976</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>IT AI&amp;S Senior Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>ClickBank</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, S3, SQS, SNS, IAM, RDS, Scala, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd7ea95be40f976</t>
+          <t>https://www.indeed.com/viewjob?jk=412f3333e8a582ca</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>IT AI&amp;S Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ClickBank</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, RDS, Scala, MySQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=412f3333e8a582ca</t>
+          <t>https://www.indeed.com/viewjob?jk=e29bb5eef54aab18</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>IT AI&amp;S Senior Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e29bb5eef54aab18</t>
+          <t>https://www.indeed.com/viewjob?jk=983aa41d463e2b8e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Analytics Engineer / Sr. Business Intelligence Engineer - Tourism Economics - Philadelphia</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Oxford Economics</t>
+          <t>The Shade Store</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ELT, dbt</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d76d14c5568ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=c80c249f67538f2f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Quality Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=983aa41d463e2b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=ffbe5145410f18d2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>The Shade Store</t>
+          <t>Intellias</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80c249f67538f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=5fc90240b32e9d4a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Database Engineer with Java MS</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Intellias</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, ECS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc90240b32e9d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=25b94269754a9820</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Database Engineer with Java MS</t>
+          <t>Intern - Cloud Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, Scala, Kafka, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b94269754a9820</t>
+          <t>https://www.indeed.com/viewjob?jk=f194b7e973e71ef2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>Mercari</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=103595c75d73a7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=69b773db1c488113</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Intern - Cloud Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, Scala, Kafka, DynamoDB, NoSQL</t>
+          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f194b7e973e71ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=65fa1c79d7085ebe</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Hadoop Infrastructure</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>LightEdge</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,147 +2411,147 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, HBase, Oozie, YARN, Spark, Scala, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57aca64828ae44c2</t>
+          <t>https://www.indeed.com/viewjob?jk=7bb7334f3f2d66e8</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr Java Developer</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Futrend Technology, Inc</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Owings Mills, MD, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66e658594e26e266</t>
+          <t>https://www.indeed.com/viewjob?jk=4b8eb10a2720f342</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Mercari</t>
+          <t>MOHELA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
+          <t>RDS, Azure, Hive, Impala, Spark, Scala, Data Modeling, ETL, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69b773db1c488113</t>
+          <t>https://www.indeed.com/viewjob?jk=00ea21484fff4c0b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Database Administrator / Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Clear Channel Outdoor</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, SQL Server, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fa1c79d7085ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=1e24a399eaddada3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SDET</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc49399df060bfe1</t>
+          <t>https://www.indeed.com/viewjob?jk=6767c0e89ecdbcae</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Distinguished Architect, Data Platform</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>LightEdge</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,59 +2596,59 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bb7334f3f2d66e8</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd1095da2d18982</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Developer III - Application Development</t>
+          <t>Software Development Engineer II - ML Platform</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Inland Empire Health Plan</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
+          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f3984b03cd26c72</t>
+          <t>https://www.indeed.com/viewjob?jk=6f38667e23fc2e6a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Owings Mills, MD, US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b8eb10a2720f342</t>
+          <t>https://www.indeed.com/viewjob?jk=c873a7854b5a7a4a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MOHELA</t>
+          <t>Waséyabek Development Company</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Otsego, MI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hive, Impala, Spark, Scala, Data Modeling, ETL, Azure DevOps, Airflow</t>
+          <t>Azure, Kafka, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00ea21484fff4c0b</t>
+          <t>https://www.indeed.com/viewjob?jk=467fe0059b658cf7</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Database Administrator / Data Engineer</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Clear Channel Outdoor</t>
+          <t>Plante Moran</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, SQL Server, ELT, dbt, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e24a399eaddada3</t>
+          <t>https://www.indeed.com/viewjob?jk=39cd370d20d11526</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Software Engineer - Full Stack (EAA - Compliance)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, MongoDB, NoSQL, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6767c0e89ecdbcae</t>
+          <t>https://www.indeed.com/viewjob?jk=4577a3ce998c3da0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Distinguished Architect, Data Platform</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
+          <t>Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd1095da2d18982</t>
+          <t>https://www.indeed.com/viewjob?jk=4c10749649c748ef</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - ML Platform</t>
+          <t>Senior Quality Platform Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Circle.so</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f38667e23fc2e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=235baa8877534de1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Burlington Stores</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>El Dorado Hills, CA, US USA</t>
+          <t>Edgewater Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
+          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c873a7854b5a7a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=d93e23fa17175252</t>
         </is>
       </c>
     </row>
@@ -2888,20 +2888,20 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Waséyabek Development Company</t>
+          <t>Fanatics</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Otsego, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Azure, Kafka, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Kinesis, Redshift, S3, RDS, Kafka, MongoDB, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=467fe0059b658cf7</t>
+          <t>https://www.indeed.com/viewjob?jk=5daf9a09c12e8d35</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Experienced Data &amp; AI Platform Cloud DevOps / DataOps Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Plante Moran</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Blob Storage, Unity Catalog, Scala, DataOps, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,129 +2946,129 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39cd370d20d11526</t>
+          <t>https://www.indeed.com/viewjob?jk=1cbeb2be8c0c0a59</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>The Clearing House Payments Company</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Liberty, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Docker</t>
+          <t>AWS, Glue, Kinesis, Scala, Kafka, Tableau, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1074f4222424a549</t>
+          <t>https://www.indeed.com/viewjob?jk=beb95949bff9aca2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack (EAA - Compliance)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, MongoDB, NoSQL, ETL, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Python</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4577a3ce998c3da0</t>
+          <t>https://www.indeed.com/viewjob?jk=648587140f4c8181</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Relias</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c10749649c748ef</t>
+          <t>https://www.indeed.com/viewjob?jk=3a059dfc3b3900d0</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Quality Platform Engineer</t>
+          <t>Senior Engineer -.NET</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Circle.so</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=235baa8877534de1</t>
+          <t>https://www.indeed.com/viewjob?jk=a13dd69a11dd2a2a</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Enterprise Data Analytics and AI Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Burlington Stores</t>
+          <t>Dudek</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Edgewater Park, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d93e23fa17175252</t>
+          <t>https://www.indeed.com/viewjob?jk=d343da250ebc576a</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Fanatics</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, RDS, Kafka, MongoDB, Tableau, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5daf9a09c12e8d35</t>
+          <t>https://www.indeed.com/viewjob?jk=7da3735857b8f1b1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Experienced Data &amp; AI Platform Cloud DevOps / DataOps Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>GreenBox Capital</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Blob Storage, Unity Catalog, Scala, DataOps, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cbeb2be8c0c0a59</t>
+          <t>https://www.indeed.com/viewjob?jk=83d3f50fcc4de14e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>The Clearing House Payments Company</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Liberty, NY, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Scala, Kafka, Tableau, CI/CD, Terraform, Git, Python</t>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beb95949bff9aca2</t>
+          <t>https://www.indeed.com/viewjob?jk=d37428d214fe7e4f</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Engineer IV, Data Engineering</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Polaris I/O</t>
+          <t>Omnicell</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,262 +3251,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, DynamoDB, Data Modeling, ELT, Kubernetes</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f266e67ee961e84e</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Senior Engineer -.NET</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a13dd69a11dd2a2a</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Enterprise Data Analytics and AI Developer</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Dudek</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d343da250ebc576a</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Solution Architect</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>HCA Healthcare</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7da3735857b8f1b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>GreenBox Capital</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=83d3f50fcc4de14e</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Engineer IV, Data Engineering</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Omnicell</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=46ffdeefe4f68e9e</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Engineer</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d37428d214fe7e4f</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Developer III - Application Development (Data Integration)</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Inland Empire Health Plan</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Rancho Cucamonga, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>RDS, Cloud Storage, HDFS, Scala, Kafka, SQL Server, MongoDB, ETL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ee815ea22a573add</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-25.xlsx
+++ b/results/job_matches_2026-03-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kiely Family of Companies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tinton Falls, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,17 +766,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8ac6e29a223b095</t>
+          <t>https://www.indeed.com/viewjob?jk=4b7a6f9f89825521</t>
         </is>
       </c>
     </row>
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b2ba9ffb9a799d</t>
+          <t>https://www.indeed.com/viewjob?jk=a8ac6e29a223b095</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Kiely Family of Companies</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tinton Falls, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d2d9cf01e65cfd8</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b2ba9ffb9a799d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cec5fe386ea9e81</t>
+          <t>https://www.indeed.com/viewjob?jk=0d2d9cf01e65cfd8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Endpoint Privilege Management Specialist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2fd5678c94e0e11</t>
+          <t>https://www.indeed.com/viewjob?jk=68341534918cf2bf</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Salesforce Service Cloud Specialist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c63d8ea7f769e54</t>
+          <t>https://www.indeed.com/viewjob?jk=d2fd5678c94e0e11</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Live Nation</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, API Gateway, RDS, Databricks, Scala, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2d1e17a962b5fca</t>
+          <t>https://www.indeed.com/viewjob?jk=22742d685387c57f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Live Nation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, API Gateway, RDS, Databricks, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15957719609ec59</t>
+          <t>https://www.indeed.com/viewjob?jk=d2d1e17a962b5fca</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Foundations Engineer</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,42 +1056,42 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73966b170bd92bef</t>
+          <t>https://www.indeed.com/viewjob?jk=d15957719609ec59</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Foundations Engineer</t>
+          <t>ETL Developer - AML &amp; Financial Crimes</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f328d78d7b80a9bf</t>
+          <t>https://www.indeed.com/viewjob?jk=cdaeb1a615542767</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19cd66b829b5339a</t>
+          <t>https://www.indeed.com/viewjob?jk=73966b170bd92bef</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a15946806730eb5d</t>
+          <t>https://www.indeed.com/viewjob?jk=f328d78d7b80a9bf</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Foundations Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Old National Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lake Elmo, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1ae7b8f4932aea6</t>
+          <t>https://www.indeed.com/viewjob?jk=19cd66b829b5339a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Data Foundations Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Augment Professional Services</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e76e474f9e2efb6</t>
+          <t>https://www.indeed.com/viewjob?jk=a15946806730eb5d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Old National Bank</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Lake Elmo, MN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70b82e4ad32cd227</t>
+          <t>https://www.indeed.com/viewjob?jk=f1ae7b8f4932aea6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IT Data Engineer - Level 3</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cintas</t>
+          <t>Augment Professional Services</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, Spark</t>
+          <t>AWS, Lambda, RDS, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2550c832064daf74</t>
+          <t>https://www.indeed.com/viewjob?jk=4e76e474f9e2efb6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IT Data Engineer - Level 3</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cintas</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, Dataflow, Hadoop, Hive, Spark</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35633737b3f1427c</t>
+          <t>https://www.indeed.com/viewjob?jk=70b82e4ad32cd227</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Insurance Integration Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Core specialty</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Informatica PowerCenter, Oracle, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5ed7b4a07ec36ef</t>
+          <t>https://www.indeed.com/viewjob?jk=f7effb39eab56def</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics and Visualization</t>
+          <t>Senior Full Stack Developer - Java</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Also</t>
+          <t>Simplain Software Solutions LLC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Walnut, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Databricks, Spark</t>
+          <t>S3, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe62c0aa52bf9aa</t>
+          <t>https://www.indeed.com/viewjob?jk=0eff7247decd592d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - Java</t>
+          <t>Sr Data Scientist</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Simplain Software Solutions LLC</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Walnut, CA, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,42 +1466,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, Power BI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eff7247decd592d</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad58dde8c86078b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr Data Scientist</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, Power BI</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad58dde8c86078b</t>
+          <t>https://www.indeed.com/viewjob?jk=073969ba933b74ce</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>Azure, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b263e0344e64430</t>
+          <t>https://www.indeed.com/viewjob?jk=799dc2ba53bfb669</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=073969ba933b74ce</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2384362c47d6ba</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Fusion Academy</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Azure, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Scala, Kafka, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=799dc2ba53bfb669</t>
+          <t>https://www.indeed.com/viewjob?jk=c239fde5950cdb3c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fusion Academy</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Scala, Kafka, Data Modeling, ELT</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c239fde5950cdb3c</t>
+          <t>https://www.indeed.com/viewjob?jk=d21a5637c26aeee6</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d21a5637c26aeee6</t>
+          <t>https://www.indeed.com/viewjob?jk=18d46da9a88bc799</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18d46da9a88bc799</t>
+          <t>https://www.indeed.com/viewjob?jk=28ea1b73fd02e910</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28ea1b73fd02e910</t>
+          <t>https://www.indeed.com/viewjob?jk=520267b51ab833b5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Sr. Software Engineer, Cloud - Platform Test</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520267b51ab833b5</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4d5281c97057bc</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>DEVELOPER L3</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>North Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77901b3684582750</t>
+          <t>https://www.indeed.com/viewjob?jk=72c2c42a5838eae6</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Cloud - Platform Test</t>
+          <t>Senior AI Engineer, MarTech</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4d5281c97057bc</t>
+          <t>https://www.indeed.com/viewjob?jk=1daebb30fd5fc85c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, MarTech</t>
+          <t>AI Product Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1daebb30fd5fc85c</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef1d9dc4f2a3c77</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DEVELOPER L3</t>
+          <t>IT AI&amp;S Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>North Quincy, MA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72c2c42a5838eae6</t>
+          <t>https://www.indeed.com/viewjob?jk=9dd7ea95be40f976</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Intellias</t>
+          <t>ClickBank</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, S3, SQS, SNS, IAM, RDS, Scala, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c59056599f6669cd</t>
+          <t>https://www.indeed.com/viewjob?jk=412f3333e8a582ca</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI Product Engineer</t>
+          <t>IT AI&amp;S Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, ELT, dbt, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef1d9dc4f2a3c77</t>
+          <t>https://www.indeed.com/viewjob?jk=e29bb5eef54aab18</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>IT AI&amp;S Senior Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd7ea95be40f976</t>
+          <t>https://www.indeed.com/viewjob?jk=983aa41d463e2b8e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ClickBank</t>
+          <t>The Shade Store</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, RDS, Scala, MySQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=412f3333e8a582ca</t>
+          <t>https://www.indeed.com/viewjob?jk=c80c249f67538f2f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>IT AI&amp;S Senior Data Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>Alderwood of North Carolina</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e29bb5eef54aab18</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f6b4e41cc2869d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Database Engineer with Java MS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,112 +2131,112 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, ECS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=983aa41d463e2b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=25b94269754a9820</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>The Shade Store</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80c249f67538f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=3154ef15f06177d4</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer</t>
+          <t>Intern - Cloud Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, Scala, Kafka, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffbe5145410f18d2</t>
+          <t>https://www.indeed.com/viewjob?jk=f194b7e973e71ef2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Intellias</t>
+          <t>Mercari</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc90240b32e9d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=69b773db1c488113</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Database Engineer with Java MS</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD</t>
+          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b94269754a9820</t>
+          <t>https://www.indeed.com/viewjob?jk=65fa1c79d7085ebe</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Intern - Cloud Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>LightEdge</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, Scala, Kafka, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f194b7e973e71ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=7bb7334f3f2d66e8</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mercari</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Owings Mills, MD, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,94 +2351,94 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69b773db1c488113</t>
+          <t>https://www.indeed.com/viewjob?jk=4b8eb10a2720f342</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>MOHELA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Hive, Impala, Spark, Scala, Data Modeling, ETL, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fa1c79d7085ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=00ea21484fff4c0b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Database Administrator / Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>LightEdge</t>
+          <t>Clear Channel Outdoor</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, SQL Server, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bb7334f3f2d66e8</t>
+          <t>https://www.indeed.com/viewjob?jk=1e24a399eaddada3</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Owings Mills, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b8eb10a2720f342</t>
+          <t>https://www.indeed.com/viewjob?jk=6767c0e89ecdbcae</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Distinguished Architect, Data Platform</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MOHELA</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hive, Impala, Spark, Scala, Data Modeling, ETL, Azure DevOps, Airflow</t>
+          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00ea21484fff4c0b</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd1095da2d18982</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Database Administrator / Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Clear Channel Outdoor</t>
+          <t>Waséyabek Development Company</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Otsego, MI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, SQL Server, ELT, dbt, CI/CD</t>
+          <t>Azure, Kafka, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e24a399eaddada3</t>
+          <t>https://www.indeed.com/viewjob?jk=467fe0059b658cf7</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6767c0e89ecdbcae</t>
+          <t>https://www.indeed.com/viewjob?jk=0b375c5df5a63eee</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Distinguished Architect, Data Platform</t>
+          <t>Software Development Engineer II - ML Platform</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd1095da2d18982</t>
+          <t>https://www.indeed.com/viewjob?jk=6f38667e23fc2e6a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - ML Platform</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f38667e23fc2e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=c873a7854b5a7a4a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Software Engineer - Full Stack (EAA - Compliance)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>El Dorado Hills, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, MongoDB, NoSQL, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c873a7854b5a7a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=4577a3ce998c3da0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Waséyabek Development Company</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Otsego, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Azure, Kafka, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=467fe0059b658cf7</t>
+          <t>https://www.indeed.com/viewjob?jk=4c10749649c748ef</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Plante Moran</t>
+          <t>Gong</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,67 +2736,67 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39cd370d20d11526</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb90cff4906f695</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack (EAA - Compliance)</t>
+          <t>Senior Quality Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Circle.so</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, MongoDB, NoSQL, ETL, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4577a3ce998c3da0</t>
+          <t>https://www.indeed.com/viewjob?jk=235baa8877534de1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Burlington Stores</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Edgewater Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c10749649c748ef</t>
+          <t>https://www.indeed.com/viewjob?jk=d93e23fa17175252</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Quality Platform Engineer</t>
+          <t>Experienced Data &amp; AI Platform Cloud DevOps / DataOps Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Circle.so</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Blob Storage, Unity Catalog, Scala, DataOps, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=235baa8877534de1</t>
+          <t>https://www.indeed.com/viewjob?jk=1cbeb2be8c0c0a59</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Burlington Stores</t>
+          <t>The Clearing House Payments Company</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Edgewater Park, NJ, US USA</t>
+          <t>Liberty, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Kinesis, Scala, Kafka, Tableau, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d93e23fa17175252</t>
+          <t>https://www.indeed.com/viewjob?jk=beb95949bff9aca2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Fanatics</t>
+          <t>Relias</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, RDS, Kafka, MongoDB, Tableau, CI/CD, Airflow</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5daf9a09c12e8d35</t>
+          <t>https://www.indeed.com/viewjob?jk=3a059dfc3b3900d0</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Experienced Data &amp; AI Platform Cloud DevOps / DataOps Engineer</t>
+          <t>Senior Engineer -.NET</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Blob Storage, Unity Catalog, Scala, DataOps, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cbeb2be8c0c0a59</t>
+          <t>https://www.indeed.com/viewjob?jk=a13dd69a11dd2a2a</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Enterprise Data Analytics and AI Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>The Clearing House Payments Company</t>
+          <t>Dudek</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Liberty, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Scala, Kafka, Tableau, CI/CD, Terraform, Git, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beb95949bff9aca2</t>
+          <t>https://www.indeed.com/viewjob?jk=d343da250ebc576a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648587140f4c8181</t>
+          <t>https://www.indeed.com/viewjob?jk=7da3735857b8f1b1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Relias</t>
+          <t>GreenBox Capital</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a059dfc3b3900d0</t>
+          <t>https://www.indeed.com/viewjob?jk=83d3f50fcc4de14e</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Engineer -.NET</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a13dd69a11dd2a2a</t>
+          <t>https://www.indeed.com/viewjob?jk=d37428d214fe7e4f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Enterprise Data Analytics and AI Developer</t>
+          <t>Engineer IV, Data Engineering</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Dudek</t>
+          <t>Omnicell</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3120,146 +3120,6 @@
         </is>
       </c>
       <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d343da250ebc576a</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Solution Architect</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>HCA Healthcare</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7da3735857b8f1b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>GreenBox Capital</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=83d3f50fcc4de14e</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Engineer</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d37428d214fe7e4f</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Engineer IV, Data Engineering</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Omnicell</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=46ffdeefe4f68e9e</t>
         </is>

--- a/results/job_matches_2026-03-25.xlsx
+++ b/results/job_matches_2026-03-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kiely Family of Companies</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tinton Falls, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,69 +836,69 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b2ba9ffb9a799d</t>
+          <t>https://www.indeed.com/viewjob?jk=0d2d9cf01e65cfd8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Endpoint Privilege Management Specialist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d2d9cf01e65cfd8</t>
+          <t>https://www.indeed.com/viewjob?jk=68341534918cf2bf</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Endpoint Privilege Management Specialist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68341534918cf2bf</t>
+          <t>https://www.indeed.com/viewjob?jk=d2fd5678c94e0e11</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Vivint</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2fd5678c94e0e11</t>
+          <t>https://www.indeed.com/viewjob?jk=9a55821b896b85e9</t>
         </is>
       </c>
     </row>
@@ -1798,25 +1798,25 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DEVELOPER L3</t>
+          <t>AI Product Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>North Quincy, MA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72c2c42a5838eae6</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef1d9dc4f2a3c77</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, MarTech</t>
+          <t>IT AI&amp;S Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1daebb30fd5fc85c</t>
+          <t>https://www.indeed.com/viewjob?jk=9dd7ea95be40f976</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Product Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>ClickBank</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, ELT, dbt, MLOps</t>
+          <t>AWS, S3, SQS, SNS, IAM, RDS, Scala, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef1d9dc4f2a3c77</t>
+          <t>https://www.indeed.com/viewjob?jk=412f3333e8a582ca</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd7ea95be40f976</t>
+          <t>https://www.indeed.com/viewjob?jk=e29bb5eef54aab18</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ClickBank</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, RDS, Scala, MySQL, DynamoDB, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=412f3333e8a582ca</t>
+          <t>https://www.indeed.com/viewjob?jk=983aa41d463e2b8e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>IT AI&amp;S Senior Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>The Shade Store</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e29bb5eef54aab18</t>
+          <t>https://www.indeed.com/viewjob?jk=c80c249f67538f2f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Alderwood of North Carolina</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=983aa41d463e2b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f6b4e41cc2869d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Database Engineer with Java MS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>The Shade Store</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,42 +2061,42 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, ECS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80c249f67538f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=25b94269754a9820</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Alderwood of North Carolina</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f6b4e41cc2869d</t>
+          <t>https://www.indeed.com/viewjob?jk=3154ef15f06177d4</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Database Engineer with Java MS</t>
+          <t>Intern - Cloud Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, Scala, Kafka, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b94269754a9820</t>
+          <t>https://www.indeed.com/viewjob?jk=f194b7e973e71ef2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>Mercari</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3154ef15f06177d4</t>
+          <t>https://www.indeed.com/viewjob?jk=69b773db1c488113</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Intern - Cloud Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>LightEdge</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, Scala, Kafka, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f194b7e973e71ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=7bb7334f3f2d66e8</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Mercari</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Owings Mills, MD, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,94 +2246,94 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69b773db1c488113</t>
+          <t>https://www.indeed.com/viewjob?jk=4b8eb10a2720f342</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>MOHELA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Hive, Impala, Spark, Scala, Data Modeling, ETL, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fa1c79d7085ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=00ea21484fff4c0b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Database Administrator / Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LightEdge</t>
+          <t>Clear Channel Outdoor</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, SQL Server, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bb7334f3f2d66e8</t>
+          <t>https://www.indeed.com/viewjob?jk=1e24a399eaddada3</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Owings Mills, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b8eb10a2720f342</t>
+          <t>https://www.indeed.com/viewjob?jk=6767c0e89ecdbcae</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MOHELA</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hive, Impala, Spark, Scala, Data Modeling, ETL, Azure DevOps, Airflow</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00ea21484fff4c0b</t>
+          <t>https://www.indeed.com/viewjob?jk=5677557f087cb138</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Database Administrator / Data Engineer</t>
+          <t>Distinguished Architect, Data Platform</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Clear Channel Outdoor</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, SQL Server, ELT, dbt, CI/CD</t>
+          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e24a399eaddada3</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd1095da2d18982</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>Waséyabek Development Company</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Otsego, MI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>Azure, Kafka, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6767c0e89ecdbcae</t>
+          <t>https://www.indeed.com/viewjob?jk=467fe0059b658cf7</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Distinguished Architect, Data Platform</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
+          <t>Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd1095da2d18982</t>
+          <t>https://www.indeed.com/viewjob?jk=0b375c5df5a63eee</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Software Development Engineer II - ML Platform</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Waséyabek Development Company</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Otsego, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, Kafka, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=467fe0059b658cf7</t>
+          <t>https://www.indeed.com/viewjob?jk=6f38667e23fc2e6a</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b375c5df5a63eee</t>
+          <t>https://www.indeed.com/viewjob?jk=c873a7854b5a7a4a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - ML Platform</t>
+          <t>Software Engineer - Full Stack (EAA - Compliance)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, MongoDB, NoSQL, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f38667e23fc2e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=4577a3ce998c3da0</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>El Dorado Hills, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
+          <t>Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,67 +2631,67 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c873a7854b5a7a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=4c10749649c748ef</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack (EAA - Compliance)</t>
+          <t>Senior Quality Platform Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Circle.so</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, MongoDB, NoSQL, ETL, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4577a3ce998c3da0</t>
+          <t>https://www.indeed.com/viewjob?jk=235baa8877534de1</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Burlington Stores</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Edgewater Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c10749649c748ef</t>
+          <t>https://www.indeed.com/viewjob?jk=d93e23fa17175252</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Experienced Data &amp; AI Platform Cloud DevOps / DataOps Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Gong</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Azure, Databricks, Blob Storage, Unity Catalog, Scala, DataOps, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb90cff4906f695</t>
+          <t>https://www.indeed.com/viewjob?jk=1cbeb2be8c0c0a59</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Quality Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Circle.so</t>
+          <t>The Clearing House Payments Company</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Liberty, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, Kinesis, Scala, Kafka, Tableau, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=235baa8877534de1</t>
+          <t>https://www.indeed.com/viewjob?jk=beb95949bff9aca2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior BI Specialist – R01562930</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Burlington Stores</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Edgewater Park, NJ, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d93e23fa17175252</t>
+          <t>https://www.indeed.com/viewjob?jk=a5053e60f58006ba</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Experienced Data &amp; AI Platform Cloud DevOps / DataOps Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Relias</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Blob Storage, Unity Catalog, Scala, DataOps, CI/CD, Jenkins, Terraform</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cbeb2be8c0c0a59</t>
+          <t>https://www.indeed.com/viewjob?jk=3a059dfc3b3900d0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer -.NET</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The Clearing House Payments Company</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Liberty, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Scala, Kafka, Tableau, CI/CD, Terraform, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beb95949bff9aca2</t>
+          <t>https://www.indeed.com/viewjob?jk=a13dd69a11dd2a2a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Enterprise Data Analytics and AI Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Relias</t>
+          <t>Dudek</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a059dfc3b3900d0</t>
+          <t>https://www.indeed.com/viewjob?jk=d343da250ebc576a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Engineer -.NET</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,29 +2936,29 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a13dd69a11dd2a2a</t>
+          <t>https://www.indeed.com/viewjob?jk=7da3735857b8f1b1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Enterprise Data Analytics and AI Developer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Dudek</t>
+          <t>GreenBox Capital</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d343da250ebc576a</t>
+          <t>https://www.indeed.com/viewjob?jk=83d3f50fcc4de14e</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Engineer IV, Data Engineering</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Omnicell</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7da3735857b8f1b1</t>
+          <t>https://www.indeed.com/viewjob?jk=46ffdeefe4f68e9e</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GreenBox Capital</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,77 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83d3f50fcc4de14e</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Engineer</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=d37428d214fe7e4f</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Engineer IV, Data Engineering</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Omnicell</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=46ffdeefe4f68e9e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-25.xlsx
+++ b/results/job_matches_2026-03-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,25 +678,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Python and PySpark, No SQL Developer-1</t>
+          <t>Cloud Engineer (Containers Focus)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=934a100fa2f03442</t>
+          <t>https://www.indeed.com/viewjob?jk=131b0feaf824cce9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Python and PySpark, No SQL Developer-1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,69 +731,69 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog, Spark</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=933ad44aa47970a9</t>
+          <t>https://www.indeed.com/viewjob?jk=934a100fa2f03442</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, Hadoop, Spark</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b7a6f9f89825521</t>
+          <t>https://www.indeed.com/viewjob?jk=933ad44aa47970a9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kiely Family of Companies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tinton Falls, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8ac6e29a223b095</t>
+          <t>https://www.indeed.com/viewjob?jk=4b7a6f9f89825521</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Kiely Family of Companies</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tinton Falls, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,69 +836,69 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d2d9cf01e65cfd8</t>
+          <t>https://www.indeed.com/viewjob?jk=a8ac6e29a223b095</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Endpoint Privilege Management Specialist</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68341534918cf2bf</t>
+          <t>https://www.indeed.com/viewjob?jk=0d2d9cf01e65cfd8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Endpoint Privilege Management Specialist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2fd5678c94e0e11</t>
+          <t>https://www.indeed.com/viewjob?jk=68341534918cf2bf</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Vivint</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a55821b896b85e9</t>
+          <t>https://www.indeed.com/viewjob?jk=d2fd5678c94e0e11</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Vivint</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22742d685387c57f</t>
+          <t>https://www.indeed.com/viewjob?jk=9a55821b896b85e9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Live Nation</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, API Gateway, RDS, Databricks, Scala, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2d1e17a962b5fca</t>
+          <t>https://www.indeed.com/viewjob?jk=22742d685387c57f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Live Nation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, API Gateway, RDS, Databricks, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15957719609ec59</t>
+          <t>https://www.indeed.com/viewjob?jk=d2d1e17a962b5fca</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ETL Developer - AML &amp; Financial Crimes</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,52 +1081,52 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdaeb1a615542767</t>
+          <t>https://www.indeed.com/viewjob?jk=d15957719609ec59</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Foundations Engineer</t>
+          <t>ETL Developer - AML &amp; Financial Crimes</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73966b170bd92bef</t>
+          <t>https://www.indeed.com/viewjob?jk=cdaeb1a615542767</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f328d78d7b80a9bf</t>
+          <t>https://www.indeed.com/viewjob?jk=73966b170bd92bef</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19cd66b829b5339a</t>
+          <t>https://www.indeed.com/viewjob?jk=f328d78d7b80a9bf</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a15946806730eb5d</t>
+          <t>https://www.indeed.com/viewjob?jk=19cd66b829b5339a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Foundations Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Old National Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lake Elmo, MN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1ae7b8f4932aea6</t>
+          <t>https://www.indeed.com/viewjob?jk=a15946806730eb5d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Augment Professional Services</t>
+          <t>Old National Bank</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Lake Elmo, MN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e76e474f9e2efb6</t>
+          <t>https://www.indeed.com/viewjob?jk=f1ae7b8f4932aea6</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Cloud - Platform Test</t>
+          <t>Data Scientist - ML Ops</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Augment Professional Services</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Jenkins</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform, AWS CloudFormation, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4d5281c97057bc</t>
+          <t>https://www.indeed.com/viewjob?jk=4e76e474f9e2efb6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI Product Engineer</t>
+          <t>Sr. Software Engineer, Cloud - Platform Test</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, ELT, dbt, MLOps</t>
+          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef1d9dc4f2a3c77</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4d5281c97057bc</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>IT AI&amp;S Senior Data Engineer</t>
+          <t>AI Product Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd7ea95be40f976</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef1d9dc4f2a3c77</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>IT AI&amp;S Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ClickBank</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, RDS, Scala, MySQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=412f3333e8a582ca</t>
+          <t>https://www.indeed.com/viewjob?jk=9dd7ea95be40f976</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>IT AI&amp;S Senior Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>ClickBank</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, S3, SQS, SNS, IAM, RDS, Scala, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e29bb5eef54aab18</t>
+          <t>https://www.indeed.com/viewjob?jk=412f3333e8a582ca</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>IT AI&amp;S Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=983aa41d463e2b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=e29bb5eef54aab18</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The Shade Store</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80c249f67538f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=983aa41d463e2b8e</t>
         </is>
       </c>
     </row>
@@ -2078,17 +2078,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
+          <t>Senior Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>Archdiocese of Chicago</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ELT, Power BI, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ELT, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3154ef15f06177d4</t>
+          <t>https://www.indeed.com/viewjob?jk=b260063a1f060a0c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Intern - Cloud Engineer</t>
+          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, Scala, Kafka, DynamoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f194b7e973e71ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=3154ef15f06177d4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Intern - Cloud Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mercari</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, Scala, Kafka, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69b773db1c488113</t>
+          <t>https://www.indeed.com/viewjob?jk=f194b7e973e71ef2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>LightEdge</t>
+          <t>Mercari</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bb7334f3f2d66e8</t>
+          <t>https://www.indeed.com/viewjob?jk=69b773db1c488113</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>LightEdge</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Owings Mills, MD, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b8eb10a2720f342</t>
+          <t>https://www.indeed.com/viewjob?jk=7bb7334f3f2d66e8</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MOHELA</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Owings Mills, MD, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hive, Impala, Spark, Scala, Data Modeling, ETL, Azure DevOps, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00ea21484fff4c0b</t>
+          <t>https://www.indeed.com/viewjob?jk=4b8eb10a2720f342</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Database Administrator / Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Clear Channel Outdoor</t>
+          <t>MOHELA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, SQL Server, ELT, dbt, CI/CD</t>
+          <t>RDS, Azure, Hive, Impala, Spark, Scala, Data Modeling, ETL, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e24a399eaddada3</t>
+          <t>https://www.indeed.com/viewjob?jk=00ea21484fff4c0b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Database Administrator / Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>Clear Channel Outdoor</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, SQL Server, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6767c0e89ecdbcae</t>
+          <t>https://www.indeed.com/viewjob?jk=1e24a399eaddada3</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5677557f087cb138</t>
+          <t>https://www.indeed.com/viewjob?jk=6767c0e89ecdbcae</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Distinguished Architect, Data Platform</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>Al Warren Oil Company, Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bensenville, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd1095da2d18982</t>
+          <t>https://www.indeed.com/viewjob?jk=b5503ca5f60f1076</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Waséyabek Development Company</t>
+          <t>Al Warren Oil Company, Inc.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Otsego, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Azure, Kafka, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=467fe0059b658cf7</t>
+          <t>https://www.indeed.com/viewjob?jk=cd4f51cd9252cb65</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b375c5df5a63eee</t>
+          <t>https://www.indeed.com/viewjob?jk=5677557f087cb138</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - ML Platform</t>
+          <t>Distinguished Architect, Data Platform</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Kubernetes</t>
+          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f38667e23fc2e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd1095da2d18982</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Waséyabek Development Company</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>El Dorado Hills, CA, US USA</t>
+          <t>Otsego, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
+          <t>Azure, Kafka, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c873a7854b5a7a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=467fe0059b658cf7</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack (EAA - Compliance)</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,29 +2586,29 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, MongoDB, NoSQL, ETL, Terraform, Kubernetes</t>
+          <t>Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4577a3ce998c3da0</t>
+          <t>https://www.indeed.com/viewjob?jk=0b375c5df5a63eee</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Software Development Engineer II - ML Platform</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c10749649c748ef</t>
+          <t>https://www.indeed.com/viewjob?jk=6f38667e23fc2e6a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Quality Platform Engineer</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Circle.so</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,67 +2666,67 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=235baa8877534de1</t>
+          <t>https://www.indeed.com/viewjob?jk=c873a7854b5a7a4a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Full Stack (EAA - Compliance)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Burlington Stores</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Edgewater Park, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, MongoDB, NoSQL, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d93e23fa17175252</t>
+          <t>https://www.indeed.com/viewjob?jk=4577a3ce998c3da0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Experienced Data &amp; AI Platform Cloud DevOps / DataOps Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Blob Storage, Unity Catalog, Scala, DataOps, CI/CD, Jenkins, Terraform</t>
+          <t>Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cbeb2be8c0c0a59</t>
+          <t>https://www.indeed.com/viewjob?jk=4c10749649c748ef</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Quality Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The Clearing House Payments Company</t>
+          <t>Circle.so</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Liberty, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Scala, Kafka, Tableau, CI/CD, Terraform, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beb95949bff9aca2</t>
+          <t>https://www.indeed.com/viewjob?jk=235baa8877534de1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior BI Specialist – R01562930</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Burlington Stores</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Edgewater Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, dbt, Power BI</t>
+          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5053e60f58006ba</t>
+          <t>https://www.indeed.com/viewjob?jk=d93e23fa17175252</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Experienced Data &amp; AI Platform Cloud DevOps / DataOps Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Relias</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Databricks, Blob Storage, Unity Catalog, Scala, DataOps, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a059dfc3b3900d0</t>
+          <t>https://www.indeed.com/viewjob?jk=1cbeb2be8c0c0a59</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Engineer -.NET</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>The Clearing House Payments Company</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Liberty, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, Kinesis, Scala, Kafka, Tableau, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a13dd69a11dd2a2a</t>
+          <t>https://www.indeed.com/viewjob?jk=beb95949bff9aca2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Enterprise Data Analytics and AI Developer</t>
+          <t>Senior BI Specialist – R01562930</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Dudek</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d343da250ebc576a</t>
+          <t>https://www.indeed.com/viewjob?jk=a5053e60f58006ba</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Relias</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7da3735857b8f1b1</t>
+          <t>https://www.indeed.com/viewjob?jk=3a059dfc3b3900d0</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Engineer -.NET</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GreenBox Capital</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83d3f50fcc4de14e</t>
+          <t>https://www.indeed.com/viewjob?jk=a13dd69a11dd2a2a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Engineer IV, Data Engineering</t>
+          <t>Enterprise Data Analytics and AI Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Omnicell</t>
+          <t>Dudek</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Python, SQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46ffdeefe4f68e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=d343da250ebc576a</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,17 +3041,122 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7da3735857b8f1b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>GreenBox Capital</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83d3f50fcc4de14e</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
           <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d37428d214fe7e4f</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Engineer IV, Data Engineering</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Omnicell</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46ffdeefe4f68e9e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-25.xlsx
+++ b/results/job_matches_2026-03-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Endpoint Privilege Management Specialist</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vivint</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68341534918cf2bf</t>
+          <t>https://www.indeed.com/viewjob?jk=9a55821b896b85e9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2fd5678c94e0e11</t>
+          <t>https://www.indeed.com/viewjob?jk=22742d685387c57f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Endpoint Privilege Management Specialist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Vivint</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a55821b896b85e9</t>
+          <t>https://www.indeed.com/viewjob?jk=68341534918cf2bf</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Live Nation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, API Gateway, RDS, Databricks, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22742d685387c57f</t>
+          <t>https://www.indeed.com/viewjob?jk=d2d1e17a962b5fca</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Live Nation</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, API Gateway, RDS, Databricks, Scala, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2d1e17a962b5fca</t>
+          <t>https://www.indeed.com/viewjob?jk=d15957719609ec59</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15957719609ec59</t>
+          <t>https://www.indeed.com/viewjob?jk=d2fd5678c94e0e11</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,42 +1126,42 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdaeb1a615542767</t>
+          <t>https://www.indeed.com/viewjob?jk=b4f8ec969f3563e7</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Foundations Engineer</t>
+          <t>ETL Developer - AML &amp; Financial Crimes</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73966b170bd92bef</t>
+          <t>https://www.indeed.com/viewjob?jk=cdaeb1a615542767</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f328d78d7b80a9bf</t>
+          <t>https://www.indeed.com/viewjob?jk=73966b170bd92bef</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19cd66b829b5339a</t>
+          <t>https://www.indeed.com/viewjob?jk=f328d78d7b80a9bf</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a15946806730eb5d</t>
+          <t>https://www.indeed.com/viewjob?jk=19cd66b829b5339a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Foundations Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Old National Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lake Elmo, MN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1ae7b8f4932aea6</t>
+          <t>https://www.indeed.com/viewjob?jk=a15946806730eb5d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Old National Bank</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Lake Elmo, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70b82e4ad32cd227</t>
+          <t>https://www.indeed.com/viewjob?jk=f1ae7b8f4932aea6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Application Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a60f5615bdba859</t>
+          <t>https://www.indeed.com/viewjob?jk=91ae67c62e9e932e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Insurance Integration Engineer</t>
+          <t>Data Engineer, Global Credit Technology</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Core specialty</t>
+          <t>The Carlyle Group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Data Factory, Databricks, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7effb39eab56def</t>
+          <t>https://www.indeed.com/viewjob?jk=178bc04a819dbf0f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - Java</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Simplain Software Solutions LLC</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Walnut, CA, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eff7247decd592d</t>
+          <t>https://www.indeed.com/viewjob?jk=6a60f5615bdba859</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr Data Scientist</t>
+          <t>Insurance Integration Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Core specialty</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, Power BI</t>
+          <t>S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad58dde8c86078b</t>
+          <t>https://www.indeed.com/viewjob?jk=f7effb39eab56def</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Full Stack Developer - Java</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Simplain Software Solutions LLC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Walnut, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark</t>
+          <t>S3, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=073969ba933b74ce</t>
+          <t>https://www.indeed.com/viewjob?jk=0eff7247decd592d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Sr Data Scientist</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Oracle, SQL Server, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=799dc2ba53bfb669</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad58dde8c86078b</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>Azure, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d21a5637c26aeee6</t>
+          <t>https://www.indeed.com/viewjob?jk=799dc2ba53bfb669</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18d46da9a88bc799</t>
+          <t>https://www.indeed.com/viewjob?jk=d21a5637c26aeee6</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28ea1b73fd02e910</t>
+          <t>https://www.indeed.com/viewjob?jk=18d46da9a88bc799</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520267b51ab833b5</t>
+          <t>https://www.indeed.com/viewjob?jk=28ea1b73fd02e910</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Scientist - ML Ops</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Augment Professional Services</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform, AWS CloudFormation, Docker</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e76e474f9e2efb6</t>
+          <t>https://www.indeed.com/viewjob?jk=520267b51ab833b5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Cloud - Platform Test</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,77 +1816,77 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Jenkins</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4d5281c97057bc</t>
+          <t>https://www.indeed.com/viewjob?jk=073969ba933b74ce</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI Product Engineer</t>
+          <t>Application Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, ELT, dbt, MLOps</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef1d9dc4f2a3c77</t>
+          <t>https://www.indeed.com/viewjob?jk=eef074d74f0c7a0b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>IT AI&amp;S Senior Data Engineer</t>
+          <t>Data Scientist - ML Ops</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>Augment Professional Services</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform, AWS CloudFormation, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd7ea95be40f976</t>
+          <t>https://www.indeed.com/viewjob?jk=4e76e474f9e2efb6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Sr. Software Engineer, Cloud - Platform Test</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ClickBank</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, RDS, Scala, MySQL, DynamoDB, CI/CD</t>
+          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=412f3333e8a582ca</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4d5281c97057bc</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>IT AI&amp;S Senior Data Engineer</t>
+          <t>AI Product Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e29bb5eef54aab18</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef1d9dc4f2a3c77</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>IT AI&amp;S Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=983aa41d463e2b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=9dd7ea95be40f976</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Alderwood of North Carolina</t>
+          <t>ClickBank</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, SQS, SNS, IAM, RDS, Scala, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f6b4e41cc2869d</t>
+          <t>https://www.indeed.com/viewjob?jk=412f3333e8a582ca</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Database Engineer with Java MS</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,42 +2061,42 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b94269754a9820</t>
+          <t>https://www.indeed.com/viewjob?jk=983aa41d463e2b8e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Full Stack Data Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Archdiocese of Chicago</t>
+          <t>Alderwood of North Carolina</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ELT, dbt, Power BI, CI/CD</t>
+          <t>IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,59 +2106,59 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b260063a1f060a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f6b4e41cc2869d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
+          <t>Database Engineer with Java MS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ELT, Power BI, CI/CD</t>
+          <t>AWS, ECS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3154ef15f06177d4</t>
+          <t>https://www.indeed.com/viewjob?jk=25b94269754a9820</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Intern - Cloud Engineer</t>
+          <t>Senior Software Engineer - Big Data</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, Scala, Kafka, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f194b7e973e71ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=365b2385af6a0f99</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Senior Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mercari</t>
+          <t>Archdiocese of Chicago</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ELT, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69b773db1c488113</t>
+          <t>https://www.indeed.com/viewjob?jk=b260063a1f060a0c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>LightEdge</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,42 +2236,42 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bb7334f3f2d66e8</t>
+          <t>https://www.indeed.com/viewjob?jk=3154ef15f06177d4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Intern - Cloud Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Owings Mills, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, Scala, Kafka, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,102 +2281,102 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b8eb10a2720f342</t>
+          <t>https://www.indeed.com/viewjob?jk=f194b7e973e71ef2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MOHELA</t>
+          <t>LERETA, LLC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pomona, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hive, Impala, Spark, Scala, Data Modeling, ETL, Azure DevOps, Airflow</t>
+          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00ea21484fff4c0b</t>
+          <t>https://www.indeed.com/viewjob?jk=d07e49add1736e55</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Database Administrator / Data Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Clear Channel Outdoor</t>
+          <t>Mercari</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, SQL Server, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e24a399eaddada3</t>
+          <t>https://www.indeed.com/viewjob?jk=69b773db1c488113</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Software &amp; Electronics Development Engineer II</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>Digital Dynamics</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Scotts Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,94 +2386,94 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6767c0e89ecdbcae</t>
+          <t>https://www.indeed.com/viewjob?jk=2e6afce3c14c5e32</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Software &amp; Electronics Development Engineer II</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>Digital Dynamics</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bensenville, IL, US USA</t>
+          <t>Scotts Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5503ca5f60f1076</t>
+          <t>https://www.indeed.com/viewjob?jk=174e2731cd487355</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>LightEdge</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd4f51cd9252cb65</t>
+          <t>https://www.indeed.com/viewjob?jk=7bb7334f3f2d66e8</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Senior Application Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, Redshift, RDS, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5677557f087cb138</t>
+          <t>https://www.indeed.com/viewjob?jk=ca736b058903f7a7</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Distinguished Architect, Data Platform</t>
+          <t>Database Administrator / Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>Clear Channel Outdoor</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, SQL Server, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd1095da2d18982</t>
+          <t>https://www.indeed.com/viewjob?jk=1e24a399eaddada3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Waséyabek Development Company</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Otsego, MI, US USA</t>
+          <t>Owings Mills, MD, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Azure, Kafka, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=467fe0059b658cf7</t>
+          <t>https://www.indeed.com/viewjob?jk=4b8eb10a2720f342</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b375c5df5a63eee</t>
+          <t>https://www.indeed.com/viewjob?jk=6767c0e89ecdbcae</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - ML Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>MOHELA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Kubernetes</t>
+          <t>RDS, Azure, Hive, Impala, Spark, Scala, Data Modeling, ETL, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f38667e23fc2e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=00ea21484fff4c0b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Intern: Financial Systems Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>El Dorado Hills, CA, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
+          <t>AWS, GCP, Scala, Snowflake, Data Modeling, dbt, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c873a7854b5a7a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=c682a9d6efe9dcdf</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack (EAA - Compliance)</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Al Warren Oil Company, Inc.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bensenville, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, MongoDB, NoSQL, ETL, Terraform, Kubernetes</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4577a3ce998c3da0</t>
+          <t>https://www.indeed.com/viewjob?jk=b5503ca5f60f1076</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Al Warren Oil Company, Inc.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,112 +2726,112 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c10749649c748ef</t>
+          <t>https://www.indeed.com/viewjob?jk=cd4f51cd9252cb65</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Quality Platform Engineer</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Circle.so</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=235baa8877534de1</t>
+          <t>https://www.indeed.com/viewjob?jk=5677557f087cb138</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Burlington Stores</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Edgewater Park, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
+          <t>Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d93e23fa17175252</t>
+          <t>https://www.indeed.com/viewjob?jk=0b375c5df5a63eee</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Experienced Data &amp; AI Platform Cloud DevOps / DataOps Engineer</t>
+          <t>Distinguished Architect, Data Platform</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Blob Storage, Unity Catalog, Scala, DataOps, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,159 +2841,159 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cbeb2be8c0c0a59</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd1095da2d18982</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Development Engineer II - ML Platform</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The Clearing House Payments Company</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Liberty, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Scala, Kafka, Tableau, CI/CD, Terraform, Git, Python</t>
+          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beb95949bff9aca2</t>
+          <t>https://www.indeed.com/viewjob?jk=6f38667e23fc2e6a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior BI Specialist – R01562930</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5053e60f58006ba</t>
+          <t>https://www.indeed.com/viewjob?jk=c873a7854b5a7a4a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Software Engineer - Full Stack (EAA - Compliance)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Relias</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, MongoDB, NoSQL, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a059dfc3b3900d0</t>
+          <t>https://www.indeed.com/viewjob?jk=4577a3ce998c3da0</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Engineer -.NET</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a13dd69a11dd2a2a</t>
+          <t>https://www.indeed.com/viewjob?jk=4c10749649c748ef</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Enterprise Data Analytics and AI Developer</t>
+          <t>Solutions Engineer(Python/Airflow)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Dudek</t>
+          <t>EDB</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d343da250ebc576a</t>
+          <t>https://www.indeed.com/viewjob?jk=f2e5544787ac4ad7</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Burlington Stores</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Edgewater Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
+          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7da3735857b8f1b1</t>
+          <t>https://www.indeed.com/viewjob?jk=d93e23fa17175252</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Experienced Data &amp; AI Platform Cloud DevOps / DataOps Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GreenBox Capital</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Databricks, Blob Storage, Unity Catalog, Scala, DataOps, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83d3f50fcc4de14e</t>
+          <t>https://www.indeed.com/viewjob?jk=1cbeb2be8c0c0a59</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d37428d214fe7e4f</t>
+          <t>https://www.indeed.com/viewjob?jk=94129ba3e4c3efdc</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Engineer IV, Data Engineering</t>
+          <t>Senior Quality Platform Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Omnicell</t>
+          <t>Circle.so</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,15 +3146,435 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=235baa8877534de1</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>S&amp;O Developer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ExxonMobil</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Spring, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd099c12f1c683af</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Data Analytics Architect</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Tampa Electric Company</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, dbt</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84060e304bd5181b</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Senior BI Specialist – R01562930</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Brillio LLC</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Virginia Beach, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a5053e60f58006ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Software Application Developer, IT</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Centurion Health</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Sterling, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22cae783634b6fb3</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Software Application Developer, IT</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Centurion Health</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Sterling, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21b9a649df292057</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Data Engineer I</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Relias</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Morrisville, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a059dfc3b3900d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Senior Engineer -.NET</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a13dd69a11dd2a2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Enterprise Data Analytics and AI Developer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Dudek</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d343da250ebc576a</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Solution Architect</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>HCA Healthcare</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7da3735857b8f1b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>GreenBox Capital</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83d3f50fcc4de14e</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d37428d214fe7e4f</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Engineer IV, Data Engineering</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Omnicell</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
           <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Python, SQL</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=46ffdeefe4f68e9e</t>
         </is>

--- a/results/job_matches_2026-03-25.xlsx
+++ b/results/job_matches_2026-03-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,35 +468,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer (GCP)</t>
+          <t>Data Architecture &amp; Engineering - Senior - Financial Services - Consulting - NYC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>24.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1224b5cebc9ca8bb</t>
+          <t>https://www.indeed.com/viewjob?jk=aca442e9dcbe994a</t>
         </is>
       </c>
     </row>
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc3a06012f008f3</t>
+          <t>https://www.indeed.com/viewjob?jk=1224b5cebc9ca8bb</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior BackEnd Engineer</t>
+          <t>Data Engineer (GCP)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,104 +556,104 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5da0b19b9bea7fb</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc3a06012f008f3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior BackEnd Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, ECS, IAM, RDS</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69b516454f937a66</t>
+          <t>https://www.indeed.com/viewjob?jk=b5da0b19b9bea7fb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ae0639bcc380726</t>
+          <t>https://www.indeed.com/viewjob?jk=69b516454f937a66</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Dataflow, Cloud Storage, Spark, Scala, Snowflake, NoSQL, Data Modeling, Kimball</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=815d21355bca9afb</t>
+          <t>https://www.indeed.com/viewjob?jk=8ae0639bcc380726</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Containers Focus)</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, HBase, YARN, Impala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=131b0feaf824cce9</t>
+          <t>https://www.indeed.com/viewjob?jk=154e5228cf0e30aa</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Python and PySpark, No SQL Developer-1</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>WellRithms</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, IAM, RDS, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=934a100fa2f03442</t>
+          <t>https://www.indeed.com/viewjob?jk=683e3c3b168935d6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer (Containers Focus)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=933ad44aa47970a9</t>
+          <t>https://www.indeed.com/viewjob?jk=131b0feaf824cce9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Python and PySpark, No SQL Developer-1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, Hadoop, Spark</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b7a6f9f89825521</t>
+          <t>https://www.indeed.com/viewjob?jk=934a100fa2f03442</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kiely Family of Companies</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tinton Falls, NJ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8ac6e29a223b095</t>
+          <t>https://www.indeed.com/viewjob?jk=933ad44aa47970a9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,69 +871,69 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d2d9cf01e65cfd8</t>
+          <t>https://www.indeed.com/viewjob?jk=4b7a6f9f89825521</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vivint</t>
+          <t>Kiely Family of Companies</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Tinton Falls, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a55821b896b85e9</t>
+          <t>https://www.indeed.com/viewjob?jk=a8ac6e29a223b095</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Vivint</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22742d685387c57f</t>
+          <t>https://www.indeed.com/viewjob?jk=9a55821b896b85e9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Endpoint Privilege Management Specialist</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68341534918cf2bf</t>
+          <t>https://www.indeed.com/viewjob?jk=22742d685387c57f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Endpoint Privilege Management Specialist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Live Nation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, API Gateway, RDS, Databricks, Scala, SQL Server</t>
+          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2d1e17a962b5fca</t>
+          <t>https://www.indeed.com/viewjob?jk=68341534918cf2bf</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Live Nation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, API Gateway, RDS, Databricks, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15957719609ec59</t>
+          <t>https://www.indeed.com/viewjob?jk=d2d1e17a962b5fca</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2fd5678c94e0e11</t>
+          <t>https://www.indeed.com/viewjob?jk=d15957719609ec59</t>
         </is>
       </c>
     </row>
@@ -1168,17 +1168,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Foundations Engineer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,17 +1186,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73966b170bd92bef</t>
+          <t>https://www.indeed.com/viewjob?jk=ad178c68fd591147</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f328d78d7b80a9bf</t>
+          <t>https://www.indeed.com/viewjob?jk=73966b170bd92bef</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19cd66b829b5339a</t>
+          <t>https://www.indeed.com/viewjob?jk=f328d78d7b80a9bf</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a15946806730eb5d</t>
+          <t>https://www.indeed.com/viewjob?jk=19cd66b829b5339a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Foundations Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Old National Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lake Elmo, MN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1ae7b8f4932aea6</t>
+          <t>https://www.indeed.com/viewjob?jk=a15946806730eb5d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Application Software Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>Old National Bank</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Lake Elmo, MN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,77 +1361,77 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91ae67c62e9e932e</t>
+          <t>https://www.indeed.com/viewjob?jk=f1ae7b8f4932aea6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer, Global Credit Technology</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>Air Methods</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Data Factory, Databricks, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=178bc04a819dbf0f</t>
+          <t>https://www.indeed.com/viewjob?jk=f9578bd5325c490c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Application Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a60f5615bdba859</t>
+          <t>https://www.indeed.com/viewjob?jk=91ae67c62e9e932e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Insurance Integration Engineer</t>
+          <t>Data Engineer, Global Credit Technology</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Core specialty</t>
+          <t>The Carlyle Group</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Data Factory, Databricks, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7effb39eab56def</t>
+          <t>https://www.indeed.com/viewjob?jk=178bc04a819dbf0f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - Java</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Simplain Software Solutions LLC</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Walnut, CA, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eff7247decd592d</t>
+          <t>https://www.indeed.com/viewjob?jk=6a60f5615bdba859</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr Data Scientist</t>
+          <t>Service Delivery Center, AI &amp; Data, Machine Learning Engineer (MLE) - Senior - Jacksonville</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,42 +1536,42 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad58dde8c86078b</t>
+          <t>https://www.indeed.com/viewjob?jk=e82e10477b4aafab</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>IBM Solution Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2384362c47d6ba</t>
+          <t>https://www.indeed.com/viewjob?jk=278169ab4c4f0734</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Insurance Integration Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fusion Academy</t>
+          <t>Core specialty</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Scala, Kafka, Data Modeling, ELT</t>
+          <t>S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,94 +1616,94 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c239fde5950cdb3c</t>
+          <t>https://www.indeed.com/viewjob?jk=f7effb39eab56def</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Senior Full Stack Developer - Java</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Simplain Software Solutions LLC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Walnut, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Oracle, SQL Server, ETL</t>
+          <t>S3, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=799dc2ba53bfb669</t>
+          <t>https://www.indeed.com/viewjob?jk=0eff7247decd592d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Sr Data Scientist</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d21a5637c26aeee6</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad58dde8c86078b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Payments Engineer Specialist – DataStage Cloud Technologies</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Hadoop, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18d46da9a88bc799</t>
+          <t>https://www.indeed.com/viewjob?jk=3fa8c98195ac4096</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28ea1b73fd02e910</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2384362c47d6ba</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Fusion Academy</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Scala, Kafka, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520267b51ab833b5</t>
+          <t>https://www.indeed.com/viewjob?jk=c239fde5950cdb3c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark</t>
+          <t>Azure, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=073969ba933b74ce</t>
+          <t>https://www.indeed.com/viewjob?jk=799dc2ba53bfb669</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Application Software Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eef074d74f0c7a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=d21a5637c26aeee6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Scientist - ML Ops</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Augment Professional Services</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform, AWS CloudFormation, Docker</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e76e474f9e2efb6</t>
+          <t>https://www.indeed.com/viewjob?jk=18d46da9a88bc799</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Cloud - Platform Test</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Jenkins</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4d5281c97057bc</t>
+          <t>https://www.indeed.com/viewjob?jk=28ea1b73fd02e910</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Product Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, ELT, dbt, MLOps</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,172 +1966,172 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef1d9dc4f2a3c77</t>
+          <t>https://www.indeed.com/viewjob?jk=520267b51ab833b5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>IT AI&amp;S Senior Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd7ea95be40f976</t>
+          <t>https://www.indeed.com/viewjob?jk=073969ba933b74ce</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Architect with Health Care Payer Domain MUST HAVE</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ClickBank</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, RDS, Scala, MySQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=412f3333e8a582ca</t>
+          <t>https://www.indeed.com/viewjob?jk=8e410146d35e333a</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Application Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=983aa41d463e2b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=eef074d74f0c7a0b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Data Scientist - ML Ops</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Alderwood of North Carolina</t>
+          <t>Augment Professional Services</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform, AWS CloudFormation, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f6b4e41cc2869d</t>
+          <t>https://www.indeed.com/viewjob?jk=4e76e474f9e2efb6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Database Engineer with Java MS</t>
+          <t>Sr. Software Engineer, Cloud - Platform Test</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD</t>
+          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,102 +2141,102 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b94269754a9820</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4d5281c97057bc</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Big Data</t>
+          <t>AI Product Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=365b2385af6a0f99</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef1d9dc4f2a3c77</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Full Stack Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Archdiocese of Chicago</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ELT, dbt, Power BI, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b260063a1f060a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=983aa41d463e2b8e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
+          <t>Databricks Automation Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ELT, Power BI, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,94 +2246,94 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3154ef15f06177d4</t>
+          <t>https://www.indeed.com/viewjob?jk=7c263ee15c9d7ff4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Intern - Cloud Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Alderwood of North Carolina</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, Scala, Kafka, DynamoDB, NoSQL</t>
+          <t>IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f194b7e973e71ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f6b4e41cc2869d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Database Engineer with Java MS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LERETA, LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Pomona, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
+          <t>AWS, ECS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d07e49add1736e55</t>
+          <t>https://www.indeed.com/viewjob?jk=25b94269754a9820</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Senior Software Engineer - Big Data</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mercari</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69b773db1c488113</t>
+          <t>https://www.indeed.com/viewjob?jk=365b2385af6a0f99</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software &amp; Electronics Development Engineer II</t>
+          <t>Senior Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Digital Dynamics</t>
+          <t>Archdiocese of Chicago</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Scotts Valley, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ELT, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e6afce3c14c5e32</t>
+          <t>https://www.indeed.com/viewjob?jk=b260063a1f060a0c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software &amp; Electronics Development Engineer II</t>
+          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Digital Dynamics</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Scotts Valley, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=174e2731cd487355</t>
+          <t>https://www.indeed.com/viewjob?jk=3154ef15f06177d4</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Intern - Cloud Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>LightEdge</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, Scala, Kafka, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,102 +2456,102 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bb7334f3f2d66e8</t>
+          <t>https://www.indeed.com/viewjob?jk=f194b7e973e71ef2</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Application Data Engineer</t>
+          <t>Software &amp; Electronics Development Engineer II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>Digital Dynamics</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Scotts Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca736b058903f7a7</t>
+          <t>https://www.indeed.com/viewjob?jk=2e6afce3c14c5e32</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Database Administrator / Data Engineer</t>
+          <t>Software &amp; Electronics Development Engineer II</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Clear Channel Outdoor</t>
+          <t>Digital Dynamics</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Scotts Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, SQL Server, ELT, dbt, CI/CD</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e24a399eaddada3</t>
+          <t>https://www.indeed.com/viewjob?jk=174e2731cd487355</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>LightEdge</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Owings Mills, MD, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b8eb10a2720f342</t>
+          <t>https://www.indeed.com/viewjob?jk=7bb7334f3f2d66e8</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Application Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, RDS, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6767c0e89ecdbcae</t>
+          <t>https://www.indeed.com/viewjob?jk=ca736b058903f7a7</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Database Administrator / Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MOHELA</t>
+          <t>Clear Channel Outdoor</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hive, Impala, Spark, Scala, Data Modeling, ETL, Azure DevOps, Airflow</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, SQL Server, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00ea21484fff4c0b</t>
+          <t>https://www.indeed.com/viewjob?jk=1e24a399eaddada3</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Intern: Financial Systems Engineer</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Owings Mills, MD, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Snowflake, Data Modeling, dbt, Jenkins, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c682a9d6efe9dcdf</t>
+          <t>https://www.indeed.com/viewjob?jk=4b8eb10a2720f342</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bensenville, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5503ca5f60f1076</t>
+          <t>https://www.indeed.com/viewjob?jk=6767c0e89ecdbcae</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>MOHELA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>RDS, Azure, Hive, Impala, Spark, Scala, Data Modeling, ETL, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd4f51cd9252cb65</t>
+          <t>https://www.indeed.com/viewjob?jk=00ea21484fff4c0b</t>
         </is>
       </c>
     </row>
@@ -2748,12 +2748,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>Al Warren Oil Company, Inc.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Bensenville, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5677557f087cb138</t>
+          <t>https://www.indeed.com/viewjob?jk=b5503ca5f60f1076</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Al Warren Oil Company, Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b375c5df5a63eee</t>
+          <t>https://www.indeed.com/viewjob?jk=cd4f51cd9252cb65</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Distinguished Architect, Data Platform</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd1095da2d18982</t>
+          <t>https://www.indeed.com/viewjob?jk=5677557f087cb138</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - ML Platform</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>ASSA ABLOY Group</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f38667e23fc2e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=e403e88df231471e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Senior Cybersecurity Analyst</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>iSynergy IT</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>El Dorado Hills, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c873a7854b5a7a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=55b3fd338a301ef7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack (EAA - Compliance)</t>
+          <t>Intern: Financial Systems Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, MongoDB, NoSQL, ETL, Terraform, Kubernetes</t>
+          <t>AWS, GCP, Scala, Snowflake, Data Modeling, dbt, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4577a3ce998c3da0</t>
+          <t>https://www.indeed.com/viewjob?jk=c682a9d6efe9dcdf</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,77 +2971,77 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Scala, Kafka, SQL Server, MySQL, MongoDB, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c10749649c748ef</t>
+          <t>https://www.indeed.com/viewjob?jk=0b375c5df5a63eee</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Solutions Engineer(Python/Airflow)</t>
+          <t>Distinguished Architect, Data Platform</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>EDB</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
+          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2e5544787ac4ad7</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd1095da2d18982</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer II - ML Platform</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Burlington Stores</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Edgewater Park, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
+          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d93e23fa17175252</t>
+          <t>https://www.indeed.com/viewjob?jk=6f38667e23fc2e6a</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Experienced Data &amp; AI Platform Cloud DevOps / DataOps Engineer</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Blob Storage, Unity Catalog, Scala, DataOps, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cbeb2be8c0c0a59</t>
+          <t>https://www.indeed.com/viewjob?jk=c873a7854b5a7a4a</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Solutions Engineer(Python/Airflow)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>EDB</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94129ba3e4c3efdc</t>
+          <t>https://www.indeed.com/viewjob?jk=f2e5544787ac4ad7</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Quality Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Circle.so</t>
+          <t>Burlington Stores</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Edgewater Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=235baa8877534de1</t>
+          <t>https://www.indeed.com/viewjob?jk=d93e23fa17175252</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S&amp;O Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd099c12f1c683af</t>
+          <t>https://www.indeed.com/viewjob?jk=94129ba3e4c3efdc</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Analytics Architect</t>
+          <t>Application Security Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Tampa Electric Company</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, dbt</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Dataflow, Oracle, CI/CD, Terraform, CloudWatch</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84060e304bd5181b</t>
+          <t>https://www.indeed.com/viewjob?jk=683a60e19be4c93b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior BI Specialist – R01562930</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5053e60f58006ba</t>
+          <t>https://www.indeed.com/viewjob?jk=ba1b325ba28e7e98</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Application Developer, IT</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Centurion Health</t>
+          <t>WellRithms</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22cae783634b6fb3</t>
+          <t>https://www.indeed.com/viewjob?jk=eb1e4c91a109f193</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Application Developer, IT</t>
+          <t>S&amp;O Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Centurion Health</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b9a649df292057</t>
+          <t>https://www.indeed.com/viewjob?jk=fd099c12f1c683af</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Data Analytics Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Relias</t>
+          <t>Tampa Electric Company</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a059dfc3b3900d0</t>
+          <t>https://www.indeed.com/viewjob?jk=84060e304bd5181b</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Engineer -.NET</t>
+          <t>Senior BI Specialist – R01562930</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,19 +3401,19 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a13dd69a11dd2a2a</t>
+          <t>https://www.indeed.com/viewjob?jk=a5053e60f58006ba</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Enterprise Data Analytics and AI Developer</t>
+          <t>Senior Technical Support Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Dudek</t>
+          <t>Kevel</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
+          <t>AWS, Athena, S3, IAM, RDS, Scala, PostgreSQL, MySQL, Git, Datadog</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d343da250ebc576a</t>
+          <t>https://www.indeed.com/viewjob?jk=cea1ef2d8d9fcfbc</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Software Application Developer, IT</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Centurion Health</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7da3735857b8f1b1</t>
+          <t>https://www.indeed.com/viewjob?jk=22cae783634b6fb3</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Software Application Developer, IT</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>GreenBox Capital</t>
+          <t>Centurion Health</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83d3f50fcc4de14e</t>
+          <t>https://www.indeed.com/viewjob?jk=21b9a649df292057</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Relias</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d37428d214fe7e4f</t>
+          <t>https://www.indeed.com/viewjob?jk=3a059dfc3b3900d0</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Engineer IV, Data Engineering</t>
+          <t>Senior Engineer -.NET</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Omnicell</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,15 +3566,120 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a13dd69a11dd2a2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Enterprise Data Analytics and AI Developer</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Dudek</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d343da250ebc576a</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Solution Architect</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>HCA Healthcare</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7da3735857b8f1b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Engineer IV, Data Engineering</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Omnicell</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
           <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Python, SQL</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=46ffdeefe4f68e9e</t>
         </is>

--- a/results/job_matches_2026-03-25.xlsx
+++ b/results/job_matches_2026-03-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,35 +468,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Architecture &amp; Engineering - Senior - Financial Services - Consulting - NYC</t>
+          <t>Data Engineer (GCP)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.3</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Spark, Scala, Spark Streaming</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aca442e9dcbe994a</t>
+          <t>https://www.indeed.com/viewjob?jk=1224b5cebc9ca8bb</t>
         </is>
       </c>
     </row>
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1224b5cebc9ca8bb</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc3a06012f008f3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer (GCP)</t>
+          <t>Senior BackEnd Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,112 +556,112 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc3a06012f008f3</t>
+          <t>https://www.indeed.com/viewjob?jk=b5da0b19b9bea7fb</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior BackEnd Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5da0b19b9bea7fb</t>
+          <t>https://www.indeed.com/viewjob?jk=69b516454f937a66</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, ECS, IAM, RDS</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69b516454f937a66</t>
+          <t>https://www.indeed.com/viewjob?jk=8ae0639bcc380726</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, HBase, YARN, Impala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ae0639bcc380726</t>
+          <t>https://www.indeed.com/viewjob?jk=154e5228cf0e30aa</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>WellRithms</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, HBase, YARN, Impala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, IAM, RDS, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154e5228cf0e30aa</t>
+          <t>https://www.indeed.com/viewjob?jk=683e3c3b168935d6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Engineer (Containers Focus)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WellRithms</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, IAM, RDS, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683e3c3b168935d6</t>
+          <t>https://www.indeed.com/viewjob?jk=131b0feaf824cce9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Containers Focus)</t>
+          <t>Python and PySpark, No SQL Developer-1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=131b0feaf824cce9</t>
+          <t>https://www.indeed.com/viewjob?jk=934a100fa2f03442</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Python and PySpark, No SQL Developer-1</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,77 +801,77 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=934a100fa2f03442</t>
+          <t>https://www.indeed.com/viewjob?jk=933ad44aa47970a9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog, Spark</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=933ad44aa47970a9</t>
+          <t>https://www.indeed.com/viewjob?jk=4b7a6f9f89825521</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vivint</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, Hadoop, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,59 +881,59 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b7a6f9f89825521</t>
+          <t>https://www.indeed.com/viewjob?jk=9a55821b896b85e9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kiely Family of Companies</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tinton Falls, NJ, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8ac6e29a223b095</t>
+          <t>https://www.indeed.com/viewjob?jk=22742d685387c57f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Endpoint Privilege Management Specialist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Vivint</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a55821b896b85e9</t>
+          <t>https://www.indeed.com/viewjob?jk=68341534918cf2bf</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Live Nation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, API Gateway, RDS, Databricks, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22742d685387c57f</t>
+          <t>https://www.indeed.com/viewjob?jk=d2d1e17a962b5fca</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Endpoint Privilege Management Specialist</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68341534918cf2bf</t>
+          <t>https://www.indeed.com/viewjob?jk=d15957719609ec59</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>ETL Developer - AML &amp; Financial Crimes</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Live Nation</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,139 +1046,139 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, API Gateway, RDS, Databricks, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2d1e17a962b5fca</t>
+          <t>https://www.indeed.com/viewjob?jk=b4f8ec969f3563e7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15957719609ec59</t>
+          <t>https://www.indeed.com/viewjob?jk=ad178c68fd591147</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ETL Developer - AML &amp; Financial Crimes</t>
+          <t>Data Foundations Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4f8ec969f3563e7</t>
+          <t>https://www.indeed.com/viewjob?jk=73966b170bd92bef</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ETL Developer - AML &amp; Financial Crimes</t>
+          <t>Data Foundations Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdaeb1a615542767</t>
+          <t>https://www.indeed.com/viewjob?jk=f328d78d7b80a9bf</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Data Foundations Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,17 +1186,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad178c68fd591147</t>
+          <t>https://www.indeed.com/viewjob?jk=19cd66b829b5339a</t>
         </is>
       </c>
     </row>
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73966b170bd92bef</t>
+          <t>https://www.indeed.com/viewjob?jk=a15946806730eb5d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Foundations Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Old National Bank</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lake Elmo, MN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f328d78d7b80a9bf</t>
+          <t>https://www.indeed.com/viewjob?jk=f1ae7b8f4932aea6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Foundations Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Air Methods</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19cd66b829b5339a</t>
+          <t>https://www.indeed.com/viewjob?jk=f9578bd5325c490c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Foundations Engineer</t>
+          <t>Senior Application Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,139 +1326,139 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a15946806730eb5d</t>
+          <t>https://www.indeed.com/viewjob?jk=91ae67c62e9e932e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Engineer, Global Credit Technology</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Old National Bank</t>
+          <t>The Carlyle Group</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lake Elmo, MN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Data Factory, Databricks, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1ae7b8f4932aea6</t>
+          <t>https://www.indeed.com/viewjob?jk=178bc04a819dbf0f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Air Methods</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9578bd5325c490c</t>
+          <t>https://www.indeed.com/viewjob?jk=6a60f5615bdba859</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Application Software Engineer</t>
+          <t>Service Delivery Center, AI &amp; Data, Machine Learning Engineer (MLE) - Senior - Jacksonville</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91ae67c62e9e932e</t>
+          <t>https://www.indeed.com/viewjob?jk=e82e10477b4aafab</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer, Global Credit Technology</t>
+          <t>Insurance Integration Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>Core specialty</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Data Factory, Databricks, Scala</t>
+          <t>S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=178bc04a819dbf0f</t>
+          <t>https://www.indeed.com/viewjob?jk=f7effb39eab56def</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Full Stack Developer - Java</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Simplain Software Solutions LLC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Walnut, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>S3, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a60f5615bdba859</t>
+          <t>https://www.indeed.com/viewjob?jk=0eff7247decd592d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Service Delivery Center, AI &amp; Data, Machine Learning Engineer (MLE) - Senior - Jacksonville</t>
+          <t>Sr Data Scientist</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,42 +1536,42 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, MLOps</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e82e10477b4aafab</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad58dde8c86078b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>IBM Solution Architect</t>
+          <t>Payments Engineer Specialist – DataStage Cloud Technologies</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB, Cassandra, NoSQL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Hadoop, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=278169ab4c4f0734</t>
+          <t>https://www.indeed.com/viewjob?jk=3fa8c98195ac4096</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Insurance Integration Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Core specialty</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7effb39eab56def</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2384362c47d6ba</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - Java</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Simplain Software Solutions LLC</t>
+          <t>Fusion Academy</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Walnut, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Scala, Kafka, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eff7247decd592d</t>
+          <t>https://www.indeed.com/viewjob?jk=c239fde5950cdb3c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr Data Scientist</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, Power BI</t>
+          <t>Azure, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad58dde8c86078b</t>
+          <t>https://www.indeed.com/viewjob?jk=799dc2ba53bfb669</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Payments Engineer Specialist – DataStage Cloud Technologies</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Hadoop, Scala, Snowflake, Oracle</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fa8c98195ac4096</t>
+          <t>https://www.indeed.com/viewjob?jk=d21a5637c26aeee6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2384362c47d6ba</t>
+          <t>https://www.indeed.com/viewjob?jk=18d46da9a88bc799</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fusion Academy</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Scala, Kafka, Data Modeling, ELT</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c239fde5950cdb3c</t>
+          <t>https://www.indeed.com/viewjob?jk=28ea1b73fd02e910</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Azure, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Oracle, SQL Server, ETL</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=799dc2ba53bfb669</t>
+          <t>https://www.indeed.com/viewjob?jk=520267b51ab833b5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d21a5637c26aeee6</t>
+          <t>https://www.indeed.com/viewjob?jk=073969ba933b74ce</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Application Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18d46da9a88bc799</t>
+          <t>https://www.indeed.com/viewjob?jk=eef074d74f0c7a0b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,147 +1921,147 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28ea1b73fd02e910</t>
+          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Data Engineer I (Snowflake)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520267b51ab833b5</t>
+          <t>https://www.indeed.com/viewjob?jk=4860f5d8874039e2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AI Product Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=073969ba933b74ce</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef1d9dc4f2a3c77</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Architect with Health Care Payer Domain MUST HAVE</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e410146d35e333a</t>
+          <t>https://www.indeed.com/viewjob?jk=983aa41d463e2b8e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Application Software Engineer</t>
+          <t>Databricks Automation Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,67 +2071,67 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eef074d74f0c7a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=7c263ee15c9d7ff4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Scientist - ML Ops</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Augment Professional Services</t>
+          <t>Alderwood of North Carolina</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform, AWS CloudFormation, Docker</t>
+          <t>IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e76e474f9e2efb6</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f6b4e41cc2869d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Cloud - Platform Test</t>
+          <t>Database Engineer with Java MS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Jenkins</t>
+          <t>AWS, ECS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,102 +2141,102 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4d5281c97057bc</t>
+          <t>https://www.indeed.com/viewjob?jk=25b94269754a9820</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AI Product Engineer</t>
+          <t>Senior Software Engineer - Big Data</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, ELT, dbt, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef1d9dc4f2a3c77</t>
+          <t>https://www.indeed.com/viewjob?jk=365b2385af6a0f99</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Archdiocese of Chicago</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ELT, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=983aa41d463e2b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=b260063a1f060a0c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Databricks Automation Engineer</t>
+          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,67 +2246,67 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c263ee15c9d7ff4</t>
+          <t>https://www.indeed.com/viewjob?jk=3154ef15f06177d4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Intern - Cloud Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Alderwood of North Carolina</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, Scala, Kafka, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f6b4e41cc2869d</t>
+          <t>https://www.indeed.com/viewjob?jk=f194b7e973e71ef2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Database Engineer with Java MS</t>
+          <t>Software &amp; Electronics Development Engineer II</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Digital Dynamics</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Scotts Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b94269754a9820</t>
+          <t>https://www.indeed.com/viewjob?jk=2e6afce3c14c5e32</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Big Data</t>
+          <t>Software &amp; Electronics Development Engineer II</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>Digital Dynamics</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Scotts Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=365b2385af6a0f99</t>
+          <t>https://www.indeed.com/viewjob?jk=174e2731cd487355</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Full Stack Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Archdiocese of Chicago</t>
+          <t>LightEdge</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,42 +2376,42 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ELT, dbt, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b260063a1f060a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=7bb7334f3f2d66e8</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
+          <t>Senior Application Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ELT, Power BI, CI/CD</t>
+          <t>AWS, Redshift, RDS, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,67 +2421,67 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3154ef15f06177d4</t>
+          <t>https://www.indeed.com/viewjob?jk=ca736b058903f7a7</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Intern - Cloud Engineer</t>
+          <t>Database Administrator / Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Clear Channel Outdoor</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, Scala, Kafka, DynamoDB, NoSQL</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, SQL Server, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f194b7e973e71ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=1e24a399eaddada3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software &amp; Electronics Development Engineer II</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Digital Dynamics</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Scotts Valley, CA, US USA</t>
+          <t>Owings Mills, MD, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,94 +2491,94 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e6afce3c14c5e32</t>
+          <t>https://www.indeed.com/viewjob?jk=4b8eb10a2720f342</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software &amp; Electronics Development Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Digital Dynamics</t>
+          <t>MOHELA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Scotts Valley, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Hive, Impala, Spark, Scala, Data Modeling, ETL, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=174e2731cd487355</t>
+          <t>https://www.indeed.com/viewjob?jk=00ea21484fff4c0b</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>LightEdge</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
+          <t>Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bb7334f3f2d66e8</t>
+          <t>https://www.indeed.com/viewjob?jk=0b375c5df5a63eee</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Application Data Engineer</t>
+          <t>Distinguished Architect, Data Platform</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca736b058903f7a7</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd1095da2d18982</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Database Administrator / Data Engineer</t>
+          <t>Software Development Engineer II - ML Platform</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Clear Channel Outdoor</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, SQL Server, ELT, dbt, CI/CD</t>
+          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e24a399eaddada3</t>
+          <t>https://www.indeed.com/viewjob?jk=6f38667e23fc2e6a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Owings Mills, MD, US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b8eb10a2720f342</t>
+          <t>https://www.indeed.com/viewjob?jk=c873a7854b5a7a4a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Intern: Financial Systems Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,29 +2691,29 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, GCP, Scala, Snowflake, Data Modeling, dbt, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6767c0e89ecdbcae</t>
+          <t>https://www.indeed.com/viewjob?jk=c682a9d6efe9dcdf</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solutions Engineer(Python/Airflow)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MOHELA</t>
+          <t>EDB</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2722,81 +2722,81 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hive, Impala, Spark, Scala, Data Modeling, ETL, Azure DevOps, Airflow</t>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00ea21484fff4c0b</t>
+          <t>https://www.indeed.com/viewjob?jk=f2e5544787ac4ad7</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>Burlington Stores</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bensenville, IL, US USA</t>
+          <t>Edgewater Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5503ca5f60f1076</t>
+          <t>https://www.indeed.com/viewjob?jk=d93e23fa17175252</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd4f51cd9252cb65</t>
+          <t>https://www.indeed.com/viewjob?jk=94129ba3e4c3efdc</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Senior Technical Support Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>Kevel</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, Athena, S3, IAM, RDS, Scala, PostgreSQL, MySQL, Git, Datadog</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5677557f087cb138</t>
+          <t>https://www.indeed.com/viewjob?jk=cea1ef2d8d9fcfbc</t>
         </is>
       </c>
     </row>
@@ -2853,20 +2853,20 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ASSA ABLOY Group</t>
+          <t>WellRithms</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e403e88df231471e</t>
+          <t>https://www.indeed.com/viewjob?jk=eb1e4c91a109f193</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Cybersecurity Analyst</t>
+          <t>Software Application Developer, IT</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>iSynergy IT</t>
+          <t>Centurion Health</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55b3fd338a301ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=22cae783634b6fb3</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Intern: Financial Systems Engineer</t>
+          <t>Software Application Developer, IT</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>Centurion Health</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Snowflake, Data Modeling, dbt, Jenkins, Docker, Jenkins, Git</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c682a9d6efe9dcdf</t>
+          <t>https://www.indeed.com/viewjob?jk=21b9a649df292057</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Data Analytics Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tampa Electric Company</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,102 +2981,102 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b375c5df5a63eee</t>
+          <t>https://www.indeed.com/viewjob?jk=84060e304bd5181b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Distinguished Architect, Data Platform</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>Relias</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd1095da2d18982</t>
+          <t>https://www.indeed.com/viewjob?jk=3a059dfc3b3900d0</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - ML Platform</t>
+          <t>Senior Engineer -.NET</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f38667e23fc2e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=a13dd69a11dd2a2a</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Enterprise Data Analytics and AI Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Dudek</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>El Dorado Hills, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c873a7854b5a7a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=d343da250ebc576a</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Solutions Engineer(Python/Airflow)</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EDB</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2e5544787ac4ad7</t>
+          <t>https://www.indeed.com/viewjob?jk=ba1b325ba28e7e98</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>S&amp;O Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Burlington Stores</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Edgewater Park, NJ, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d93e23fa17175252</t>
+          <t>https://www.indeed.com/viewjob?jk=fd099c12f1c683af</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior BI Specialist – R01562930</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94129ba3e4c3efdc</t>
+          <t>https://www.indeed.com/viewjob?jk=a5053e60f58006ba</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Application Security Architect</t>
+          <t>Engineer IV, Data Engineering</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Omnicell</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,470 +3216,15 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Dataflow, Oracle, CI/CD, Terraform, CloudWatch</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=683a60e19be4c93b</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>BI Developer</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Star Schema</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ba1b325ba28e7e98</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>WellRithms</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eb1e4c91a109f193</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>S&amp;O Developer</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>ExxonMobil</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Spring, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd099c12f1c683af</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Data Analytics Architect</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Tampa Electric Company</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, dbt</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=84060e304bd5181b</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Senior BI Specialist – R01562930</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Brillio LLC</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Virginia Beach, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, dbt, Power BI</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a5053e60f58006ba</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Senior Technical Support Engineer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Kevel</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, Athena, S3, IAM, RDS, Scala, PostgreSQL, MySQL, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cea1ef2d8d9fcfbc</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Software Application Developer, IT</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Centurion Health</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Sterling, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=22cae783634b6fb3</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Software Application Developer, IT</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Centurion Health</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Sterling, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=21b9a649df292057</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Data Engineer I</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Relias</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Morrisville, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3a059dfc3b3900d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Senior Engineer -.NET</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a13dd69a11dd2a2a</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Enterprise Data Analytics and AI Developer</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Dudek</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d343da250ebc576a</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Solution Architect</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>HCA Healthcare</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7da3735857b8f1b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Engineer IV, Data Engineering</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Omnicell</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=46ffdeefe4f68e9e</t>
         </is>

--- a/results/job_matches_2026-03-25.xlsx
+++ b/results/job_matches_2026-03-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Python and PySpark, No SQL Developer-1</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=934a100fa2f03442</t>
+          <t>https://www.indeed.com/viewjob?jk=933ad44aa47970a9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,17 +801,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, PostgreSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=933ad44aa47970a9</t>
+          <t>https://www.indeed.com/viewjob?jk=dd6782d769bbb10c</t>
         </is>
       </c>
     </row>
@@ -853,25 +853,25 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Vivint</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a55821b896b85e9</t>
+          <t>https://www.indeed.com/viewjob?jk=b2ac379ca55b9cb0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Endpoint Privilege Management Specialist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22742d685387c57f</t>
+          <t>https://www.indeed.com/viewjob?jk=68341534918cf2bf</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Endpoint Privilege Management Specialist</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vivint</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68341534918cf2bf</t>
+          <t>https://www.indeed.com/viewjob?jk=9a55821b896b85e9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Live Nation</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, API Gateway, RDS, Databricks, Scala, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2d1e17a962b5fca</t>
+          <t>https://www.indeed.com/viewjob?jk=22742d685387c57f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Live Nation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, API Gateway, RDS, Databricks, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15957719609ec59</t>
+          <t>https://www.indeed.com/viewjob?jk=d2d1e17a962b5fca</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ETL Developer - AML &amp; Financial Crimes</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4f8ec969f3563e7</t>
+          <t>https://www.indeed.com/viewjob?jk=d15957719609ec59</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>ETL Developer - AML &amp; Financial Crimes</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,59 +1091,59 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad178c68fd591147</t>
+          <t>https://www.indeed.com/viewjob?jk=b4f8ec969f3563e7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Foundations Engineer</t>
+          <t>ETL Developer - AML &amp; Financial Crimes</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73966b170bd92bef</t>
+          <t>https://www.indeed.com/viewjob?jk=cdaeb1a615542767</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Foundations Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Air Methods</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f328d78d7b80a9bf</t>
+          <t>https://www.indeed.com/viewjob?jk=f9578bd5325c490c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Foundations Engineer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,17 +1186,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19cd66b829b5339a</t>
+          <t>https://www.indeed.com/viewjob?jk=ad178c68fd591147</t>
         </is>
       </c>
     </row>
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a15946806730eb5d</t>
+          <t>https://www.indeed.com/viewjob?jk=73966b170bd92bef</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Foundations Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Old National Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lake Elmo, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1ae7b8f4932aea6</t>
+          <t>https://www.indeed.com/viewjob?jk=f328d78d7b80a9bf</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Foundations Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Air Methods</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9578bd5325c490c</t>
+          <t>https://www.indeed.com/viewjob?jk=19cd66b829b5339a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Application Software Engineer</t>
+          <t>Data Foundations Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,77 +1326,77 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91ae67c62e9e932e</t>
+          <t>https://www.indeed.com/viewjob?jk=a15946806730eb5d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer, Global Credit Technology</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>Old National Bank</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Lake Elmo, MN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Data Factory, Databricks, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=178bc04a819dbf0f</t>
+          <t>https://www.indeed.com/viewjob?jk=f1ae7b8f4932aea6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Application Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a60f5615bdba859</t>
+          <t>https://www.indeed.com/viewjob?jk=91ae67c62e9e932e</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Insurance Integration Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Core specialty</t>
+          <t>Insight</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, Azure, Data Factory, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7effb39eab56def</t>
+          <t>https://www.indeed.com/viewjob?jk=b8c469fe05779639</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - Java</t>
+          <t>Data Engineer, Global Credit Technology</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Simplain Software Solutions LLC</t>
+          <t>The Carlyle Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Walnut, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Data Factory, Databricks, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eff7247decd592d</t>
+          <t>https://www.indeed.com/viewjob?jk=178bc04a819dbf0f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr Data Scientist</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, Power BI</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,19 +1546,19 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad58dde8c86078b</t>
+          <t>https://www.indeed.com/viewjob?jk=6a60f5615bdba859</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Payments Engineer Specialist – DataStage Cloud Technologies</t>
+          <t>Insurance Integration Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Core specialty</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1567,11 +1567,11 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Hadoop, Scala, Snowflake, Oracle</t>
+          <t>S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,67 +1581,67 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fa8c98195ac4096</t>
+          <t>https://www.indeed.com/viewjob?jk=f7effb39eab56def</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Full Stack Developer - Java</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Simplain Software Solutions LLC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Walnut, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>S3, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2384362c47d6ba</t>
+          <t>https://www.indeed.com/viewjob?jk=0eff7247decd592d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Data Scientist</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fusion Academy</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Scala, Kafka, Data Modeling, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c239fde5950cdb3c</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad58dde8c86078b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Senior Software Engineer- Java- Big Data</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Azure, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Oracle, SQL Server, ETL</t>
+          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=799dc2ba53bfb669</t>
+          <t>https://www.indeed.com/viewjob?jk=aaac56b41d3197f1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Senior Software Engineer- Java- Big Data</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d21a5637c26aeee6</t>
+          <t>https://www.indeed.com/viewjob?jk=2beb81df979d35f8</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18d46da9a88bc799</t>
+          <t>https://www.indeed.com/viewjob?jk=073969ba933b74ce</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>Azure, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28ea1b73fd02e910</t>
+          <t>https://www.indeed.com/viewjob?jk=799dc2ba53bfb669</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Payments Engineer Specialist – DataStage Cloud Technologies</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Hadoop, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520267b51ab833b5</t>
+          <t>https://www.indeed.com/viewjob?jk=3fa8c98195ac4096</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=073969ba933b74ce</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2384362c47d6ba</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Application Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>Fusion Academy</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Scala, Kafka, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eef074d74f0c7a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=c239fde5950cdb3c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,77 +1921,77 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=d21a5637c26aeee6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer I (Snowflake)</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Snowflake, Data Modeling, ELT</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4860f5d8874039e2</t>
+          <t>https://www.indeed.com/viewjob?jk=18d46da9a88bc799</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI Product Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, ELT, dbt, MLOps</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,67 +2001,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef1d9dc4f2a3c77</t>
+          <t>https://www.indeed.com/viewjob?jk=28ea1b73fd02e910</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=983aa41d463e2b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=520267b51ab833b5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Databricks Automation Engineer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,102 +2071,102 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c263ee15c9d7ff4</t>
+          <t>https://www.indeed.com/viewjob?jk=7540039fe27c9ab2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Sr. Software Engineer, Cloud - Platform Test</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Alderwood of North Carolina</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f6b4e41cc2869d</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4d5281c97057bc</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Database Engineer with Java MS</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b94269754a9820</t>
+          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Big Data</t>
+          <t>Application Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=365b2385af6a0f99</t>
+          <t>https://www.indeed.com/viewjob?jk=eef074d74f0c7a0b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Full Stack Data Engineer</t>
+          <t>QA Automation Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Archdiocese of Chicago</t>
+          <t>Core specialty</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ELT, dbt, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Spark, Scala, SQL Server, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b260063a1f060a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=8a8c0b028e6bca22</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
+          <t>Databricks Automation Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ELT, Power BI, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,67 +2246,67 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3154ef15f06177d4</t>
+          <t>https://www.indeed.com/viewjob?jk=7c263ee15c9d7ff4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Intern - Cloud Engineer</t>
+          <t>Data Engineer I (Snowflake)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, Scala, Kafka, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f194b7e973e71ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=4860f5d8874039e2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software &amp; Electronics Development Engineer II</t>
+          <t>AI Product Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Digital Dynamics</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Scotts Valley, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,137 +2316,137 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e6afce3c14c5e32</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef1d9dc4f2a3c77</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software &amp; Electronics Development Engineer II</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Digital Dynamics</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Scotts Valley, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=174e2731cd487355</t>
+          <t>https://www.indeed.com/viewjob?jk=983aa41d463e2b8e</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>LightEdge</t>
+          <t>Alderwood of North Carolina</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
+          <t>IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bb7334f3f2d66e8</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f6b4e41cc2869d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Application Data Engineer</t>
+          <t>Database Engineer with Java MS</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, ECS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca736b058903f7a7</t>
+          <t>https://www.indeed.com/viewjob?jk=25b94269754a9820</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Database Administrator / Data Engineer</t>
+          <t>Senior Software Engineer - Big Data</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Clear Channel Outdoor</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, SQL Server, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,207 +2456,207 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e24a399eaddada3</t>
+          <t>https://www.indeed.com/viewjob?jk=365b2385af6a0f99</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Senior Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Archdiocese of Chicago</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Owings Mills, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ELT, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b8eb10a2720f342</t>
+          <t>https://www.indeed.com/viewjob?jk=b260063a1f060a0c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MOHELA</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hive, Impala, Spark, Scala, Data Modeling, ETL, Azure DevOps, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00ea21484fff4c0b</t>
+          <t>https://www.indeed.com/viewjob?jk=3154ef15f06177d4</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Intern - Cloud Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, Scala, Kafka, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b375c5df5a63eee</t>
+          <t>https://www.indeed.com/viewjob?jk=f194b7e973e71ef2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Distinguished Architect, Data Platform</t>
+          <t>AI DevOps and Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd1095da2d18982</t>
+          <t>https://www.indeed.com/viewjob?jk=2828050f215fd3ad</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - ML Platform</t>
+          <t>Associate Network Security Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f38667e23fc2e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=1cf26dea742dfb68</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Software &amp; Electronics Development Engineer II</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Digital Dynamics</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>El Dorado Hills, CA, US USA</t>
+          <t>Scotts Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,137 +2666,137 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c873a7854b5a7a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=2e6afce3c14c5e32</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Intern: Financial Systems Engineer</t>
+          <t>Software &amp; Electronics Development Engineer II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>Digital Dynamics</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Scotts Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Snowflake, Data Modeling, dbt, Jenkins, Docker, Jenkins, Git</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c682a9d6efe9dcdf</t>
+          <t>https://www.indeed.com/viewjob?jk=174e2731cd487355</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Solutions Engineer(Python/Airflow)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>EDB</t>
+          <t>LightEdge</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2e5544787ac4ad7</t>
+          <t>https://www.indeed.com/viewjob?jk=7bb7334f3f2d66e8</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Burlington Stores</t>
+          <t>MOHELA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Edgewater Park, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Hive, Impala, Spark, Scala, Data Modeling, ETL, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d93e23fa17175252</t>
+          <t>https://www.indeed.com/viewjob?jk=00ea21484fff4c0b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94129ba3e4c3efdc</t>
+          <t>https://www.indeed.com/viewjob?jk=f1fa666427f4129e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Technical Support Engineer</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Kevel</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, IAM, RDS, Scala, PostgreSQL, MySQL, Git, Datadog</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cea1ef2d8d9fcfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=c750325324ef95ac</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Application Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>WellRithms</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb1e4c91a109f193</t>
+          <t>https://www.indeed.com/viewjob?jk=ca736b058903f7a7</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Application Developer, IT</t>
+          <t>Database Administrator / Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Centurion Health</t>
+          <t>Clear Channel Outdoor</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, SQL Server, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22cae783634b6fb3</t>
+          <t>https://www.indeed.com/viewjob?jk=1e24a399eaddada3</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Application Developer, IT</t>
+          <t>Cognos Optimization Specialist</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Centurion Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Databricks, Scala, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b9a649df292057</t>
+          <t>https://www.indeed.com/viewjob?jk=6958a876172ec730</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Analytics Architect</t>
+          <t>Cognos Optimization Specialist</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tampa Electric Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, dbt</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Databricks, Scala, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,67 +2981,67 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84060e304bd5181b</t>
+          <t>https://www.indeed.com/viewjob?jk=39930f1669a9c233</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Distinguished Architect, Data Platform</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Relias</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a059dfc3b3900d0</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd1095da2d18982</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Engineer -.NET</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a13dd69a11dd2a2a</t>
+          <t>https://www.indeed.com/viewjob?jk=0b375c5df5a63eee</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Enterprise Data Analytics and AI Developer</t>
+          <t>Software Development Engineer II - ML Platform</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Dudek</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
+          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,67 +3086,67 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d343da250ebc576a</t>
+          <t>https://www.indeed.com/viewjob?jk=6f38667e23fc2e6a</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba1b325ba28e7e98</t>
+          <t>https://www.indeed.com/viewjob?jk=c873a7854b5a7a4a</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S&amp;O Developer</t>
+          <t>Intern: Financial Systems Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, GCP, Scala, Snowflake, Data Modeling, dbt, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd099c12f1c683af</t>
+          <t>https://www.indeed.com/viewjob?jk=c682a9d6efe9dcdf</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior BI Specialist – R01562930</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5053e60f58006ba</t>
+          <t>https://www.indeed.com/viewjob?jk=94129ba3e4c3efdc</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Engineer IV, Data Engineering</t>
+          <t>Solutions Engineer(Python/Airflow)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Omnicell</t>
+          <t>EDB</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,17 +3216,577 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Python, SQL</t>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f2e5544787ac4ad7</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Administration &amp; Infrastructure</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fea1ea320a3da1b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Cognos Business Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>NY, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a5f0f39ab230c0b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Cognos Business Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>NY, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6124d6f05994ef55</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Administration &amp; Infrastructure</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6596f101bae22a82</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Sarasota, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5bd5bde56b916bab</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>WellRithms</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb1e4c91a109f193</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Software Application Developer, IT</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Centurion Health</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Sterling, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22cae783634b6fb3</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Software Application Developer, IT</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Centurion Health</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Sterling, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21b9a649df292057</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Data Analytics Architect</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Tampa Electric Company</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, dbt</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84060e304bd5181b</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Data Engineer I</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Relias</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Morrisville, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a059dfc3b3900d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Senior Engineer -.NET</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a13dd69a11dd2a2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Enterprise Data Analytics and AI Developer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Dudek</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, Power BI, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=46ffdeefe4f68e9e</t>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d343da250ebc576a</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>BI Developer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Star Schema</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba1b325ba28e7e98</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior Business Intelligence Developer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Somerville, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Oracle, SQL Server, MySQL, Dimensional Modeling, ETL, Talend, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d53ca27d22c29c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>S&amp;O Developer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>ExxonMobil</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Spring, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd099c12f1c683af</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Senior BI Specialist – R01562930</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Brillio LLC</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Virginia Beach, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a5053e60f58006ba</t>
         </is>
       </c>
     </row>
